--- a/sndk/dist/20261025_SanDisk模型_v0.1.xlsx
+++ b/sndk/dist/20261025_SanDisk模型_v0.1.xlsx
@@ -7774,7 +7774,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -19570,7 +19570,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -20370,7 +20370,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -25115,7 +25115,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
   </si>
   <si>

--- a/sndk/dist/20261025_SanDisk模型_v0.1.xlsx
+++ b/sndk/dist/20261025_SanDisk模型_v0.1.xlsx
@@ -25666,7 +25666,7 @@
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="str">
         <f aca="false">"1. 加權目標價 "&amp;TEXT(Val!B49,"#,##0")&amp;" 美元，相對現價 "&amp;TEXT(px,"#,##0.00")&amp;"（2026-10-23 收盤）"&amp;TEXT(Val!B52,"+0.0%;−0.0%")&amp;"，主因是 Comparable 偏低：同業前瞻 P/B 中位數 "&amp;TEXT(Val!B32,"0.00")&amp;"x，而共識目標價隱含約 "&amp;TEXT(cons_tp/((cons_bv28+cons_bv29)/2),"0.00")&amp;"x（倍數因素 "&amp;TEXT(Val!B59,"+0%;−0%")&amp;"）；DCF 目標價 "&amp;TEXT(Val!B24,"#,##0")&amp;" 高於 Comparable "&amp;TEXT(Val!B34,"#,##0")&amp;"。"</f>
-        <v>1. 加權目標價 953 美元，相對現價 1,238.03（2026-10-23 收盤）−23.0%，主因是 Comparable 偏低：同業前瞻 P/B 中位數 1.49x，而共識目標價隱含約 3.56x（倍數因素 +139%）；DCF 目標價 1,139 高於 Comparable 767。</v>
+        <v>1. 加權目標價 955 美元，相對現價 1,238.03（2026-10-23 收盤）−22.9%，主因是 Comparable 偏低：同業前瞻 P/B 中位數 1.49x，而共識目標價隱含約 3.56x（倍數因素 +139%）；DCF 目標價 1,142 高於 Comparable 767。</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25684,7 +25684,7 @@
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="str">
         <f aca="false">"投資建議："&amp;Val!B55&amp;"（依上檔空間固定規則；上檔空間："&amp;TEXT(Val!B52,"+0.0%;−0.0%")&amp;"，級距："&amp;Val!B54&amp;"）"</f>
-        <v>投資建議：中立（依上檔空間固定規則；上檔空間：−23.0%，級距：0%～−25%）</v>
+        <v>投資建議：中立（依上檔空間固定規則；上檔空間：−22.9%，級距：0%～−25%）</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28059,28 +28059,28 @@
         <v>15.2424811606062</v>
       </c>
       <c r="S4" s="16" t="n">
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="T4" s="16" t="n">
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="U4" s="16" t="n">
-        <v>15.943778925719</v>
+        <v>16.0087785772089</v>
       </c>
       <c r="V4" s="16" t="n">
-        <v>16.2388346960649</v>
+        <v>16.319990053314</v>
       </c>
       <c r="W4" s="16" t="n">
-        <v>15.8788556672779</v>
+        <v>16.1040315346425</v>
       </c>
       <c r="X4" s="16" t="n">
-        <v>15.8917081703626</v>
+        <v>16.1855444682125</v>
       </c>
       <c r="Y4" s="16" t="n">
-        <v>15.9045710763906</v>
+        <v>16.2674699915322</v>
       </c>
       <c r="Z4" s="16" t="n">
-        <v>15.9174443937821</v>
+        <v>16.3498101929854</v>
       </c>
       <c r="AA4" s="8" t="s">
         <v>302</v>
@@ -28142,28 +28142,28 @@
         <v>5.22803660760145</v>
       </c>
       <c r="S5" s="16" t="n">
-        <v>5.78331322430948</v>
+        <v>5.84881998029706</v>
       </c>
       <c r="T5" s="16" t="n">
-        <v>6.36321490653485</v>
+        <v>6.46508042853906</v>
       </c>
       <c r="U5" s="16" t="n">
-        <v>6.86790680566433</v>
+        <v>7.01015362169591</v>
       </c>
       <c r="V5" s="16" t="n">
-        <v>7.41262782793176</v>
+        <v>7.60118212649694</v>
       </c>
       <c r="W5" s="16" t="n">
-        <v>7.16589400090849</v>
+        <v>7.30322767592516</v>
       </c>
       <c r="X5" s="16" t="n">
-        <v>7.16460761675993</v>
+        <v>7.30342891315223</v>
       </c>
       <c r="Y5" s="16" t="n">
-        <v>7.16332146353638</v>
+        <v>7.3036301559243</v>
       </c>
       <c r="Z5" s="16" t="n">
-        <v>7.1620355411964</v>
+        <v>7.30383140424153</v>
       </c>
       <c r="AA5" s="8" t="s">
         <v>304</v>
@@ -28225,28 +28225,28 @@
         <v>2.86571668276147</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>3.04469115475764</v>
+        <v>3.0738536547637</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>3.31317412872458</v>
+        <v>3.3579323857844</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>3.70834160627888</v>
+        <v>3.77307261513255</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>4.22750505731519</v>
+        <v>4.31804644883388</v>
       </c>
       <c r="W6" s="16" t="n">
-        <v>4.07746231168348</v>
+        <v>4.14347788935371</v>
       </c>
       <c r="X6" s="16" t="n">
-        <v>4.06792229460515</v>
+        <v>4.13464957769195</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>4.0584045982545</v>
+        <v>4.12584007609481</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>4.04890917040784</v>
+        <v>4.11704934448456</v>
       </c>
       <c r="AA6" s="8" t="s">
         <v>306</v>
@@ -28308,28 +28308,28 @@
         <v>57.0362619279465</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>65.3689409417794</v>
+        <v>65.635437259828</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>68.6377931678167</v>
+        <v>68.9808180664366</v>
       </c>
       <c r="W7" s="16" t="n">
-        <v>69.2958113229694</v>
+        <v>70.2784856885749</v>
       </c>
       <c r="X7" s="16" t="n">
-        <v>71.6040679350321</v>
+        <v>72.9280209051894</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>73.9892130124351</v>
+        <v>75.6774449682311</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>76.4538077245352</v>
+        <v>78.5305237388133</v>
       </c>
       <c r="AA7" s="8" t="s">
         <v>309</v>
@@ -28391,28 +28391,28 @@
         <v>49.7460314816301</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>52.4091644300165</v>
+        <v>53.0027954876253</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>54.9183920812081</v>
+        <v>55.7975531278103</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>57.5477556566027</v>
+        <v>58.7396741324276</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>60.3030069819771</v>
+        <v>61.8369287499111</v>
       </c>
       <c r="W8" s="16" t="n">
-        <v>60.1889108462319</v>
+        <v>61.3424255815484</v>
       </c>
       <c r="X8" s="16" t="n">
-        <v>62.1323596182698</v>
+        <v>63.3362349972848</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>64.1385606992701</v>
+        <v>65.3948490885553</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>66.2095403079513</v>
+        <v>67.5203741980913</v>
       </c>
       <c r="AA8" s="8" t="s">
         <v>311</v>
@@ -28474,28 +28474,28 @@
         <v>40.6599563952741</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>43.1993191560824</v>
+        <v>43.6130885931507</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>44.7701571691272</v>
+        <v>45.374965164521</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>46.3981148801541</v>
+        <v>47.2080178243746</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>48.0852693078439</v>
+        <v>49.1151219362044</v>
       </c>
       <c r="W9" s="16" t="n">
-        <v>47.8847477956092</v>
+        <v>48.660019041713</v>
       </c>
       <c r="X9" s="16" t="n">
-        <v>49.3241067797042</v>
+        <v>50.1331840918391</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>50.8067311954965</v>
+        <v>51.6509486983906</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>52.3339215507821</v>
+        <v>53.2146630973327</v>
       </c>
       <c r="AA9" s="8" t="s">
         <v>313</v>
@@ -28836,7 +28836,7 @@
       </c>
       <c r="G5" s="15" t="n">
         <f aca="false">G55</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="G6" s="14" t="n">
         <f aca="false">G57</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">G59</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28908,7 +28908,7 @@
       </c>
       <c r="G8" s="14" t="n">
         <f aca="false">G60</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28936,7 +28936,7 @@
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">G61</f>
-        <v>44.2370988034375</v>
+        <v>44.2983742512942</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28964,7 +28964,7 @@
       </c>
       <c r="G10" s="15" t="n">
         <f aca="false">G69</f>
-        <v>406.942436087428</v>
+        <v>407.591295072546</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28988,7 +28988,7 @@
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">G70</f>
-        <v>829.486479257523</v>
+        <v>830.005886376082</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29012,7 +29012,7 @@
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">G64</f>
-        <v>40.7128597630642</v>
+        <v>40.7691095626112</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29045,7 +29045,7 @@
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">G91</f>
-        <v>22.9705482306035</v>
+        <v>23.1378213739785</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">G93</f>
-        <v>0.676966372448314</v>
+        <v>0.677075411574218</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">G95</f>
-        <v>12.8693407064255</v>
+        <v>12.9834291958883</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29117,7 +29117,7 @@
       </c>
       <c r="G18" s="14" t="n">
         <f aca="false">G96</f>
-        <v>0.560253964216659</v>
+        <v>0.561134472690238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29145,7 +29145,7 @@
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">G97</f>
-        <v>12.1339309767543</v>
+        <v>12.2309061927977</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">G105</f>
-        <v>96.263879822199</v>
+        <v>97.0602642508936</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29197,7 +29197,7 @@
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">G106</f>
-        <v>495.963483261656</v>
+        <v>496.567398989591</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="G22" s="15" t="n">
         <f aca="false">G100</f>
-        <v>10.9156980829181</v>
+        <v>11.002636910359</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29254,7 +29254,7 @@
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">G127</f>
-        <v>12.7894883355406</v>
+        <v>12.8633653093348</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29278,7 +29278,7 @@
       </c>
       <c r="G26" s="14" t="n">
         <f aca="false">G129</f>
-        <v>0.494968733211702</v>
+        <v>0.494929682153329</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="G27" s="15" t="n">
         <f aca="false">G131</f>
-        <v>3.75125943642389</v>
+        <v>3.7865851307888</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29326,7 +29326,7 @@
       </c>
       <c r="G28" s="14" t="n">
         <f aca="false">G132</f>
-        <v>0.293308014989117</v>
+        <v>0.294369711170444</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29354,7 +29354,7 @@
       </c>
       <c r="G29" s="15" t="n">
         <f aca="false">G133</f>
-        <v>4.33216925004039</v>
+        <v>4.36219609025055</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29382,7 +29382,7 @@
       </c>
       <c r="G30" s="15" t="n">
         <f aca="false">G141</f>
-        <v>33.2799019603142</v>
+        <v>33.5132305555486</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="G31" s="15" t="n">
         <f aca="false">G142</f>
-        <v>430.088230508421</v>
+        <v>430.266506574784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29430,7 +29430,7 @@
       </c>
       <c r="G32" s="15" t="n">
         <f aca="false">G136</f>
-        <v>3.72479994990795</v>
+        <v>3.75039417169047</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29572,11 +29572,11 @@
       </c>
       <c r="Q42" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R42" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T42" s="8" t="s">
         <v>358</v>
@@ -29647,11 +29647,11 @@
       </c>
       <c r="Q43" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R43" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29719,11 +29719,11 @@
       </c>
       <c r="Q44" s="13" t="n">
         <f aca="false">Q42*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R44" s="13" t="n">
         <f aca="false">R42*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T44" s="5" t="s">
         <v>360</v>
@@ -29866,11 +29866,11 @@
       </c>
       <c r="Q46" s="13" t="n">
         <f aca="false">Q43*Q45</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R46" s="13" t="n">
         <f aca="false">R43*R45</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29938,11 +29938,11 @@
       </c>
       <c r="Q47" s="14" t="n">
         <f aca="false">1-Q46/Q44</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R47" s="14" t="n">
         <f aca="false">1-R46/R44</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30010,11 +30010,11 @@
       </c>
       <c r="Q48" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q44</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R48" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R44</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T48" s="5" t="s">
         <v>365</v>
@@ -30085,11 +30085,11 @@
       </c>
       <c r="Q49" s="13" t="n">
         <f aca="false">Q44-Q46-Q48</f>
-        <v>12.5916316304418</v>
+        <v>12.6211954306263</v>
       </c>
       <c r="R49" s="13" t="n">
         <f aca="false">R44-R46-R48</f>
-        <v>12.8358500150521</v>
+        <v>12.8783749770521</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30157,11 +30157,11 @@
       </c>
       <c r="Q51" s="13" t="n">
         <f aca="false">(Q49+rf*$F67/4)*(1-tax)</f>
-        <v>11.0574974278717</v>
+        <v>11.0826266580284</v>
       </c>
       <c r="R51" s="13" t="n">
         <f aca="false">(R49+rf*$F67/4)*(1-tax)</f>
-        <v>11.2650830547904</v>
+        <v>11.3012292724904</v>
       </c>
       <c r="T51" s="5" t="s">
         <v>366</v>
@@ -30216,11 +30216,11 @@
       </c>
       <c r="Q52" s="15" t="n">
         <f aca="false">Q51/(sh0+dil)*1000</f>
-        <v>71.338693083043</v>
+        <v>71.5008171485706</v>
       </c>
       <c r="R52" s="15" t="n">
         <f aca="false">R51/(sh0+dil)*1000</f>
-        <v>72.6779551921961</v>
+        <v>72.9111565967123</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="G55" s="13" t="n">
         <f aca="false">SUM(O44:R44)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="G56" s="13" t="n">
         <f aca="false">SUM(O46:R46)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="G57" s="14" t="n">
         <f aca="false">1-G56/G55</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30358,7 +30358,7 @@
       </c>
       <c r="G58" s="13" t="n">
         <f aca="false">SUM(O48:R48)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="G59" s="13" t="n">
         <f aca="false">SUM(O49:R49)</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30406,7 +30406,7 @@
       </c>
       <c r="G60" s="14" t="n">
         <f aca="false">G59/G55</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30434,7 +30434,7 @@
       </c>
       <c r="G61" s="13" t="n">
         <f aca="false">SUM(O51:R51)</f>
-        <v>44.2370988034375</v>
+        <v>44.2983742512942</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30481,7 +30481,7 @@
       </c>
       <c r="G63" s="13" t="n">
         <f aca="false">cap_r*G55</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T63" s="8" t="s">
         <v>371</v>
@@ -30508,7 +30508,7 @@
       </c>
       <c r="G64" s="13" t="n">
         <f aca="false">G61+G62-G63</f>
-        <v>40.7128597630642</v>
+        <v>40.7691095626112</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30531,7 +30531,7 @@
       </c>
       <c r="G65" s="13" t="n">
         <f aca="false">MAX(0,payout*G64)</f>
-        <v>20.3564298815321</v>
+        <v>20.3845547813056</v>
       </c>
       <c r="T65" s="8" t="s">
         <v>374</v>
@@ -30558,7 +30558,7 @@
       </c>
       <c r="G66" s="13" t="n">
         <f aca="false">F66+G61-G65</f>
-        <v>83.0531924643841</v>
+        <v>83.0863430124674</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30582,7 +30582,7 @@
       </c>
       <c r="G67" s="13" t="n">
         <f aca="false">F67+G64-G65</f>
-        <v>62.0753171751934</v>
+        <v>62.1034420749669</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="G68" s="20" t="n">
         <f aca="false">F68-G65/bb_px*1000</f>
-        <v>100.126035253432</v>
+        <v>100.103317791195</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30634,7 +30634,7 @@
       </c>
       <c r="G69" s="15" t="n">
         <f aca="false">G61/(G68+dil)*1000</f>
-        <v>406.942436087428</v>
+        <v>407.591295072546</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30658,7 +30658,7 @@
       </c>
       <c r="G70" s="15" t="n">
         <f aca="false">G66/G68*1000</f>
-        <v>829.486479257523</v>
+        <v>830.005886376082</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30682,7 +30682,7 @@
       </c>
       <c r="G71" s="21" t="n">
         <f aca="false">G61/G66</f>
-        <v>0.53263574211681</v>
+        <v>0.533160717455661</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="G72" s="15" t="n">
         <f aca="false">G64/(G68+dil)*1000</f>
-        <v>374.522533805488</v>
+        <v>375.118375029163</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30847,11 +30847,11 @@
       </c>
       <c r="Q78" s="13" t="n">
         <f aca="false">Units!S5*1*1</f>
-        <v>5.78331322430948</v>
+        <v>5.84881998029706</v>
       </c>
       <c r="R78" s="13" t="n">
         <f aca="false">Units!T5*1*1</f>
-        <v>6.36321490653485</v>
+        <v>6.46508042853906</v>
       </c>
       <c r="T78" s="8" t="s">
         <v>358</v>
@@ -30922,11 +30922,11 @@
       </c>
       <c r="Q79" s="13" t="n">
         <f aca="false">Units!S8*1</f>
-        <v>52.4091644300165</v>
+        <v>53.0027954876253</v>
       </c>
       <c r="R79" s="13" t="n">
         <f aca="false">Units!T8*1</f>
-        <v>54.9183920812081</v>
+        <v>55.7975531278103</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30994,11 +30994,11 @@
       </c>
       <c r="Q80" s="13" t="n">
         <f aca="false">Q78*sd_k</f>
-        <v>5.77988776731581</v>
+        <v>5.84535572364536</v>
       </c>
       <c r="R80" s="13" t="n">
         <f aca="false">R78*sd_k</f>
-        <v>6.35944597371756</v>
+        <v>6.46125116076303</v>
       </c>
       <c r="T80" s="5" t="s">
         <v>360</v>
@@ -31141,11 +31141,11 @@
       </c>
       <c r="Q82" s="13" t="n">
         <f aca="false">Q79*Q81</f>
-        <v>1.86812157311593</v>
+        <v>1.88928151713052</v>
       </c>
       <c r="R82" s="13" t="n">
         <f aca="false">R79*R81</f>
-        <v>1.89599147978877</v>
+        <v>1.92634345825265</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31285,11 +31285,11 @@
       </c>
       <c r="Q84" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q80</f>
-        <v>0.677734055693812</v>
+        <v>0.678388735257108</v>
       </c>
       <c r="R84" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R80</f>
-        <v>0.69847856189313</v>
+        <v>0.699496613763585</v>
       </c>
       <c r="T84" s="5" t="s">
         <v>365</v>
@@ -31360,11 +31360,11 @@
       </c>
       <c r="Q85" s="13" t="n">
         <f aca="false">Q80-Q82-Q84</f>
-        <v>3.23403213850607</v>
+        <v>3.27768547125773</v>
       </c>
       <c r="R85" s="13" t="n">
         <f aca="false">R80-R82-R84</f>
-        <v>3.76497593203566</v>
+        <v>3.83541108874679</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31432,11 +31432,11 @@
       </c>
       <c r="Q87" s="13" t="n">
         <f aca="false">(Q85+rf*$F103/4)*(1-tax)</f>
-        <v>3.04767516180331</v>
+        <v>3.08478049464222</v>
       </c>
       <c r="R87" s="13" t="n">
         <f aca="false">(R85+rf*$F103/4)*(1-tax)</f>
-        <v>3.49897738630346</v>
+        <v>3.55884726950792</v>
       </c>
       <c r="T87" s="5" t="s">
         <v>366</v>
@@ -31491,11 +31491,11 @@
       </c>
       <c r="Q88" s="15" t="n">
         <f aca="false">Q87/(sh0+dil)*1000</f>
-        <v>19.662420398731</v>
+        <v>19.901809642853</v>
       </c>
       <c r="R88" s="15" t="n">
         <f aca="false">R87/(sh0+dil)*1000</f>
-        <v>22.5740476535707</v>
+        <v>22.9603049645672</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31561,7 +31561,7 @@
       </c>
       <c r="G91" s="13" t="n">
         <f aca="false">SUM(O80:R80)</f>
-        <v>22.9705482306035</v>
+        <v>23.1378213739785</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="G92" s="13" t="n">
         <f aca="false">SUM(O82:R82)</f>
-        <v>7.42025952178279</v>
+        <v>7.47177144426127</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="G93" s="14" t="n">
         <f aca="false">1-G92/G91</f>
-        <v>0.676966372448314</v>
+        <v>0.677075411574218</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31633,7 +31633,7 @@
       </c>
       <c r="G94" s="13" t="n">
         <f aca="false">SUM(O84:R84)</f>
-        <v>2.68094800239512</v>
+        <v>2.68262073382887</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31657,7 +31657,7 @@
       </c>
       <c r="G95" s="13" t="n">
         <f aca="false">SUM(O85:R85)</f>
-        <v>12.8693407064255</v>
+        <v>12.9834291958883</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31681,7 +31681,7 @@
       </c>
       <c r="G96" s="14" t="n">
         <f aca="false">G95/G91</f>
-        <v>0.560253964216659</v>
+        <v>0.561134472690238</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31709,7 +31709,7 @@
       </c>
       <c r="G97" s="13" t="n">
         <f aca="false">SUM(O87:R87)</f>
-        <v>12.1339309767543</v>
+        <v>12.2309061927977</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31756,7 +31756,7 @@
       </c>
       <c r="G99" s="13" t="n">
         <f aca="false">cap_r*G91</f>
-        <v>1.37823289383621</v>
+        <v>1.38826928243871</v>
       </c>
       <c r="T99" s="8" t="s">
         <v>371</v>
@@ -31783,7 +31783,7 @@
       </c>
       <c r="G100" s="13" t="n">
         <f aca="false">G97+G98-G99</f>
-        <v>10.9156980829181</v>
+        <v>11.002636910359</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31806,7 +31806,7 @@
       </c>
       <c r="G101" s="13" t="n">
         <f aca="false">MAX(0,payout*G100)</f>
-        <v>5.45784904145905</v>
+        <v>5.50131845517948</v>
       </c>
       <c r="T101" s="8" t="s">
         <v>374</v>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="G102" s="13" t="n">
         <f aca="false">F102+G97-G101</f>
-        <v>58.2601550648979</v>
+        <v>58.3136608672209</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31857,7 +31857,7 @@
       </c>
       <c r="G103" s="13" t="n">
         <f aca="false">F103+G100-G101</f>
-        <v>40.6046542265352</v>
+        <v>40.6481236402556</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31881,7 +31881,7 @@
       </c>
       <c r="G104" s="20" t="n">
         <f aca="false">F104-G101/bb_px*1000</f>
-        <v>117.468638379898</v>
+        <v>117.433526618696</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31909,7 +31909,7 @@
       </c>
       <c r="G105" s="15" t="n">
         <f aca="false">G97/(G104+dil)*1000</f>
-        <v>96.263879822199</v>
+        <v>97.0602642508936</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31933,7 +31933,7 @@
       </c>
       <c r="G106" s="15" t="n">
         <f aca="false">G102/G104*1000</f>
-        <v>495.963483261656</v>
+        <v>496.567398989591</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31957,7 +31957,7 @@
       </c>
       <c r="G107" s="21" t="n">
         <f aca="false">G97/G102</f>
-        <v>0.208271518729017</v>
+        <v>0.20974341193648</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31977,7 +31977,7 @@
       </c>
       <c r="G108" s="15" t="n">
         <f aca="false">G100/(G104+dil)*1000</f>
-        <v>86.5990955810192</v>
+        <v>87.3131417363772</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32122,11 +32122,11 @@
       </c>
       <c r="Q114" s="13" t="n">
         <f aca="false">Units!S6*1*1</f>
-        <v>3.04469115475764</v>
+        <v>3.0738536547637</v>
       </c>
       <c r="R114" s="13" t="n">
         <f aca="false">Units!T6*1*1</f>
-        <v>3.31317412872458</v>
+        <v>3.3579323857844</v>
       </c>
       <c r="T114" s="8" t="s">
         <v>358</v>
@@ -32197,11 +32197,11 @@
       </c>
       <c r="Q115" s="13" t="n">
         <f aca="false">Units!S9*1</f>
-        <v>43.1993191560824</v>
+        <v>43.6130885931507</v>
       </c>
       <c r="R115" s="13" t="n">
         <f aca="false">Units!T9*1</f>
-        <v>44.7701571691272</v>
+        <v>45.374965164521</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32269,11 +32269,11 @@
       </c>
       <c r="Q116" s="13" t="n">
         <f aca="false">Q114*sd_k</f>
-        <v>3.04288778388612</v>
+        <v>3.07203301094054</v>
       </c>
       <c r="R116" s="13" t="n">
         <f aca="false">R114*sd_k</f>
-        <v>3.31121173536107</v>
+        <v>3.35594348210082</v>
       </c>
       <c r="T116" s="5" t="s">
         <v>360</v>
@@ -32416,11 +32416,11 @@
       </c>
       <c r="Q118" s="13" t="n">
         <f aca="false">Q115*Q117</f>
-        <v>1.62882488340896</v>
+        <v>1.64442600787706</v>
       </c>
       <c r="R118" s="13" t="n">
         <f aca="false">R115*R117</f>
-        <v>1.64417007539836</v>
+        <v>1.66638146062159</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32492,7 +32492,7 @@
       </c>
       <c r="R119" s="14" t="n">
         <f aca="false">1-R118/R116</f>
-        <v>0.503453657813559</v>
+        <v>0.503453657813558</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32560,11 +32560,11 @@
       </c>
       <c r="Q120" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q116</f>
-        <v>0.650364055859515</v>
+        <v>0.65065550813006</v>
       </c>
       <c r="R120" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R116</f>
-        <v>0.667996219509565</v>
+        <v>0.668443536976963</v>
       </c>
       <c r="T120" s="5" t="s">
         <v>365</v>
@@ -32635,11 +32635,11 @@
       </c>
       <c r="Q121" s="13" t="n">
         <f aca="false">Q116-Q118-Q120</f>
-        <v>0.763698844617637</v>
+        <v>0.776951494933426</v>
       </c>
       <c r="R121" s="13" t="n">
         <f aca="false">R116-R118-R120</f>
-        <v>0.999045440453149</v>
+        <v>1.02111848450226</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32707,11 +32707,11 @@
       </c>
       <c r="Q123" s="13" t="n">
         <f aca="false">(Q121+rf*$F139/4)*(1-tax)</f>
-        <v>0.935043700195011</v>
+        <v>0.946308452963431</v>
       </c>
       <c r="R123" s="13" t="n">
         <f aca="false">(R121+rf*$F139/4)*(1-tax)</f>
-        <v>1.1350883066552</v>
+        <v>1.15385039409694</v>
       </c>
       <c r="T123" s="5" t="s">
         <v>366</v>
@@ -32766,11 +32766,11 @@
       </c>
       <c r="Q124" s="15" t="n">
         <f aca="false">Q123/(sh0+dil)*1000</f>
-        <v>6.03254000125813</v>
+        <v>6.10521582557053</v>
       </c>
       <c r="R124" s="15" t="n">
         <f aca="false">R123/(sh0+dil)*1000</f>
-        <v>7.32315036551739</v>
+        <v>7.44419609094802</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32836,7 +32836,7 @@
       </c>
       <c r="G127" s="13" t="n">
         <f aca="false">SUM(O116:R116)</f>
-        <v>12.7894883355406</v>
+        <v>12.8633653093348</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32860,7 +32860,7 @@
       </c>
       <c r="G128" s="13" t="n">
         <f aca="false">SUM(O118:R118)</f>
-        <v>6.45909149567225</v>
+        <v>6.49690400536357</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32884,7 +32884,7 @@
       </c>
       <c r="G129" s="14" t="n">
         <f aca="false">1-G128/G127</f>
-        <v>0.494968733211702</v>
+        <v>0.494929682153329</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32908,7 +32908,7 @@
       </c>
       <c r="G130" s="13" t="n">
         <f aca="false">SUM(O120:R120)</f>
-        <v>2.57913740344449</v>
+        <v>2.57987617318244</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="G131" s="13" t="n">
         <f aca="false">SUM(O121:R121)</f>
-        <v>3.75125943642389</v>
+        <v>3.7865851307888</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32956,7 +32956,7 @@
       </c>
       <c r="G132" s="14" t="n">
         <f aca="false">G131/G127</f>
-        <v>0.293308014989117</v>
+        <v>0.294369711170444</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="G133" s="13" t="n">
         <f aca="false">SUM(O123:R123)</f>
-        <v>4.33216925004039</v>
+        <v>4.36219609025055</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="G135" s="13" t="n">
         <f aca="false">cap_r*G127</f>
-        <v>0.767369300132438</v>
+        <v>0.771801918560088</v>
       </c>
       <c r="T135" s="8" t="s">
         <v>371</v>
@@ -33058,7 +33058,7 @@
       </c>
       <c r="G136" s="13" t="n">
         <f aca="false">G133+G134-G135</f>
-        <v>3.72479994990795</v>
+        <v>3.75039417169047</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33081,7 +33081,7 @@
       </c>
       <c r="G137" s="13" t="n">
         <f aca="false">MAX(0,payout*G136)</f>
-        <v>1.86239997495397</v>
+        <v>1.87519708584523</v>
       </c>
       <c r="T137" s="8" t="s">
         <v>374</v>
@@ -33108,7 +33108,7 @@
       </c>
       <c r="G138" s="13" t="n">
         <f aca="false">F138+G133-G137</f>
-        <v>52.2960357671419</v>
+        <v>52.3132654964608</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33132,7 +33132,7 @@
       </c>
       <c r="G139" s="13" t="n">
         <f aca="false">F139+G136-G137</f>
-        <v>35.4976567126033</v>
+        <v>35.5104538234946</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33156,7 +33156,7 @@
       </c>
       <c r="G140" s="20" t="n">
         <f aca="false">F140-G137/bb_px*1000</f>
-        <v>121.593738348341</v>
+        <v>121.58340167565</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="G141" s="15" t="n">
         <f aca="false">G133/(G140+dil)*1000</f>
-        <v>33.2799019603142</v>
+        <v>33.5132305555486</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33208,7 +33208,7 @@
       </c>
       <c r="G142" s="15" t="n">
         <f aca="false">G138/G140*1000</f>
-        <v>430.088230508421</v>
+        <v>430.266506574784</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33232,7 +33232,7 @@
       </c>
       <c r="G143" s="21" t="n">
         <f aca="false">G133/G138</f>
-        <v>0.0828393431068121</v>
+        <v>0.0833860407843527</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33252,7 +33252,7 @@
       </c>
       <c r="G144" s="15" t="n">
         <f aca="false">G136/(G140+dil)*1000</f>
-        <v>28.614066071764</v>
+        <v>28.8129698779381</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33335,19 +33335,19 @@
       </c>
       <c r="F152" s="15" t="n">
         <f aca="false">G5</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
       <c r="G152" s="22" t="n">
         <f aca="false">F152*(1+G153)</f>
-        <v>63.3785838534408</v>
+        <v>63.5219746196495</v>
       </c>
       <c r="H152" s="22" t="n">
         <f aca="false">G152*(1+H153)</f>
-        <v>66.2989904097488</v>
+        <v>66.4783984833485</v>
       </c>
       <c r="I152" s="22" t="n">
         <f aca="false">H152*(1+I153)</f>
-        <v>70.2769298343337</v>
+        <v>70.4671023923494</v>
       </c>
       <c r="J152" s="8" t="s">
         <v>391</v>
@@ -33370,15 +33370,15 @@
       </c>
       <c r="F153" s="14" t="n">
         <f aca="false">F152/E152-1</f>
-        <v>0.0182362800845102</v>
+        <v>0.0196252500682417</v>
       </c>
       <c r="G153" s="23" t="n">
         <f aca="false">$F153+(fade_gA-$F153)*1/3</f>
-        <v>0.0321575200563401</v>
+        <v>0.0330835000454945</v>
       </c>
       <c r="H153" s="23" t="n">
         <f aca="false">$F153+(fade_gA-$F153)*2/3</f>
-        <v>0.0460787600281701</v>
+        <v>0.0465417500227472</v>
       </c>
       <c r="I153" s="23" t="n">
         <f aca="false">$F153+(fade_gA-$F153)*3/3</f>
@@ -33406,15 +33406,15 @@
       </c>
       <c r="F154" s="14" t="n">
         <f aca="false">F155/F152</f>
-        <v>0.720427176174029</v>
+        <v>0.720442331836705</v>
       </c>
       <c r="G154" s="23" t="n">
         <f aca="false">$F154+(fade_mA-$F154)*1/3</f>
-        <v>0.538936238590238</v>
+        <v>0.538946342365355</v>
       </c>
       <c r="H154" s="23" t="n">
         <f aca="false">$F154+(fade_mA-$F154)*2/3</f>
-        <v>0.357445301006446</v>
+        <v>0.357450352894004</v>
       </c>
       <c r="I154" s="23" t="n">
         <f aca="false">$F154+(fade_mA-$F154)*3/3</f>
@@ -33442,19 +33442,19 @@
       </c>
       <c r="F155" s="15" t="n">
         <f aca="false">G9</f>
-        <v>44.2370988034375</v>
+        <v>44.2983742512942</v>
       </c>
       <c r="G155" s="22" t="n">
         <f aca="false">G152*G154</f>
-        <v>34.1570155891494</v>
+        <v>34.234935881085</v>
       </c>
       <c r="H155" s="22" t="n">
         <f aca="false">H152*H154</f>
-        <v>23.6982625834361</v>
+        <v>23.7627269977012</v>
       </c>
       <c r="I155" s="22" t="n">
         <f aca="false">I152*I154</f>
-        <v>12.3655324522987</v>
+        <v>12.3989941436848</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33478,19 +33478,19 @@
       </c>
       <c r="F156" s="15" t="n">
         <f aca="false">G10</f>
-        <v>406.942436087428</v>
+        <v>407.591295072546</v>
       </c>
       <c r="G156" s="22" t="n">
         <f aca="false">$F156*G155/$F155</f>
-        <v>314.214528287388</v>
+        <v>314.997154824239</v>
       </c>
       <c r="H156" s="22" t="n">
         <f aca="false">$F156*H155/$F155</f>
-        <v>218.003191158495</v>
+        <v>218.641899057174</v>
       </c>
       <c r="I156" s="22" t="n">
         <f aca="false">$F156*I155/$F155</f>
-        <v>113.752032474281</v>
+        <v>114.083691919546</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33519,19 +33519,19 @@
       </c>
       <c r="F159" s="15" t="n">
         <f aca="false">G15</f>
-        <v>22.9705482306035</v>
+        <v>23.1378213739785</v>
       </c>
       <c r="G159" s="22" t="n">
         <f aca="false">F159*(1+G160)</f>
-        <v>16.1759288288852</v>
+        <v>16.3539648156067</v>
       </c>
       <c r="H159" s="22" t="n">
         <f aca="false">G159*(1+H160)</f>
-        <v>14.107051743893</v>
+        <v>14.283606823495</v>
       </c>
       <c r="I159" s="22" t="n">
         <f aca="false">H159*(1+I160)</f>
-        <v>14.6713338136487</v>
+        <v>14.8549510964348</v>
       </c>
       <c r="J159" s="8" t="s">
         <v>391</v>
@@ -33554,15 +33554,15 @@
       </c>
       <c r="F160" s="14" t="n">
         <f aca="false">F159/E159-1</f>
-        <v>-0.463695509582953</v>
+        <v>-0.459790102667211</v>
       </c>
       <c r="G160" s="23" t="n">
         <f aca="false">$F160+(fade_gB-$F160)*1/3</f>
-        <v>-0.295797006388636</v>
+        <v>-0.293193401778141</v>
       </c>
       <c r="H160" s="23" t="n">
         <f aca="false">$F160+(fade_gB-$F160)*2/3</f>
-        <v>-0.127898503194318</v>
+        <v>-0.12659670088907</v>
       </c>
       <c r="I160" s="23" t="n">
         <f aca="false">$F160+(fade_gB-$F160)*3/3</f>
@@ -33590,15 +33590,15 @@
       </c>
       <c r="F161" s="14" t="n">
         <f aca="false">F162/F159</f>
-        <v>0.528238632136275</v>
+        <v>0.528610969680704</v>
       </c>
       <c r="G161" s="23" t="n">
         <f aca="false">$F161+(fade_mB-$F161)*1/3</f>
-        <v>0.401035300152698</v>
+        <v>0.401283525182317</v>
       </c>
       <c r="H161" s="23" t="n">
         <f aca="false">$F161+(fade_mB-$F161)*2/3</f>
-        <v>0.273831968169122</v>
+        <v>0.273956080683931</v>
       </c>
       <c r="I161" s="23" t="n">
         <f aca="false">$F161+(fade_mB-$F161)*3/3</f>
@@ -33626,19 +33626,19 @@
       </c>
       <c r="F162" s="15" t="n">
         <f aca="false">G19</f>
-        <v>12.1339309767543</v>
+        <v>12.2309061927977</v>
       </c>
       <c r="G162" s="22" t="n">
         <f aca="false">G159*G161</f>
-        <v>6.48711847314065</v>
+        <v>6.56257665191426</v>
       </c>
       <c r="H162" s="22" t="n">
         <f aca="false">H159*H161</f>
-        <v>3.86296174409385</v>
+        <v>3.91308094339495</v>
       </c>
       <c r="I162" s="22" t="n">
         <f aca="false">I159*I161</f>
-        <v>2.15123766811818</v>
+        <v>2.1781612198732</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33662,19 +33662,19 @@
       </c>
       <c r="F163" s="15" t="n">
         <f aca="false">G20</f>
-        <v>96.263879822199</v>
+        <v>97.0602642508936</v>
       </c>
       <c r="G163" s="22" t="n">
         <f aca="false">$F163*G162/$F162</f>
-        <v>51.4652007075962</v>
+        <v>52.0783508565072</v>
       </c>
       <c r="H163" s="22" t="n">
         <f aca="false">$F163*H162/$F162</f>
-        <v>30.6465963753712</v>
+        <v>31.0528643106349</v>
       </c>
       <c r="I163" s="22" t="n">
         <f aca="false">$F163*I162/$F162</f>
-        <v>17.0667267474526</v>
+        <v>17.2851381777775</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33703,19 +33703,19 @@
       </c>
       <c r="F166" s="15" t="n">
         <f aca="false">G25</f>
-        <v>12.7894883355406</v>
+        <v>12.8633653093348</v>
       </c>
       <c r="G166" s="22" t="n">
         <f aca="false">F166*(1+G167)</f>
-        <v>7.13919090079623</v>
+        <v>7.19664323964815</v>
       </c>
       <c r="H166" s="22" t="n">
         <f aca="false">G166*(1+H167)</f>
-        <v>5.63356303486828</v>
+        <v>5.68343440518888</v>
       </c>
       <c r="I166" s="22" t="n">
         <f aca="false">H166*(1+I167)</f>
-        <v>5.74623429556564</v>
+        <v>5.79710309329266</v>
       </c>
       <c r="J166" s="8" t="s">
         <v>391</v>
@@ -33738,15 +33738,15 @@
       </c>
       <c r="F167" s="14" t="n">
         <f aca="false">F166/E166-1</f>
-        <v>-0.672688446148721</v>
+        <v>-0.670797769488951</v>
       </c>
       <c r="G167" s="23" t="n">
         <f aca="false">$F167+(fade_gC-$F167)*1/3</f>
-        <v>-0.44179229743248</v>
+        <v>-0.440531846325967</v>
       </c>
       <c r="H167" s="23" t="n">
         <f aca="false">$F167+(fade_gC-$F167)*2/3</f>
-        <v>-0.21089614871624</v>
+        <v>-0.210265923162984</v>
       </c>
       <c r="I167" s="23" t="n">
         <f aca="false">$F167+(fade_gC-$F167)*3/3</f>
@@ -33774,15 +33774,15 @@
       </c>
       <c r="F168" s="14" t="n">
         <f aca="false">F169/F166</f>
-        <v>0.338728894884852</v>
+        <v>0.339117795798348</v>
       </c>
       <c r="G168" s="23" t="n">
         <f aca="false">$F168+(fade_mC-$F168)*1/3</f>
-        <v>0.264920232906047</v>
+        <v>0.265179500181711</v>
       </c>
       <c r="H168" s="23" t="n">
         <f aca="false">$F168+(fade_mC-$F168)*2/3</f>
-        <v>0.191111570927241</v>
+        <v>0.191241204565073</v>
       </c>
       <c r="I168" s="23" t="n">
         <f aca="false">$F168+(fade_mC-$F168)*3/3</f>
@@ -33810,19 +33810,19 @@
       </c>
       <c r="F169" s="15" t="n">
         <f aca="false">G29</f>
-        <v>4.33216925004039</v>
+        <v>4.36219609025055</v>
       </c>
       <c r="G169" s="22" t="n">
         <f aca="false">G166*G168</f>
-        <v>1.89131611619967</v>
+        <v>1.90840225727598</v>
       </c>
       <c r="H169" s="22" t="n">
         <f aca="false">H166*H168</f>
-        <v>1.07663908151131</v>
+        <v>1.0869068417149</v>
       </c>
       <c r="I169" s="22" t="n">
         <f aca="false">I166*I168</f>
-        <v>0.674049998369117</v>
+        <v>0.680017056317206</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33846,19 +33846,19 @@
       </c>
       <c r="F170" s="15" t="n">
         <f aca="false">G30</f>
-        <v>33.2799019603142</v>
+        <v>33.5132305555486</v>
       </c>
       <c r="G170" s="22" t="n">
         <f aca="false">$F170*G169/$F169</f>
-        <v>14.5291680195783</v>
+        <v>14.6615886855159</v>
       </c>
       <c r="H170" s="22" t="n">
         <f aca="false">$F170*H169/$F169</f>
-        <v>8.27078560677316</v>
+        <v>8.35032603422065</v>
       </c>
       <c r="I170" s="22" t="n">
         <f aca="false">$F170*I169/$F169</f>
-        <v>5.17807974881523</v>
+        <v>5.22433378017975</v>
       </c>
     </row>
   </sheetData>
@@ -33971,15 +33971,15 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">PL!F156</f>
-        <v>406.942436087428</v>
+        <v>407.591295072546</v>
       </c>
       <c r="C10" s="15" t="n">
         <f aca="false">PL!F163</f>
-        <v>96.263879822199</v>
+        <v>97.0602642508936</v>
       </c>
       <c r="D10" s="15" t="n">
         <f aca="false">PL!F170</f>
-        <v>33.2799019603142</v>
+        <v>33.5132305555486</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33988,15 +33988,15 @@
       </c>
       <c r="B11" s="15" t="n">
         <f aca="false">PL!G156</f>
-        <v>314.214528287388</v>
+        <v>314.997154824239</v>
       </c>
       <c r="C11" s="15" t="n">
         <f aca="false">PL!G163</f>
-        <v>51.4652007075962</v>
+        <v>52.0783508565072</v>
       </c>
       <c r="D11" s="15" t="n">
         <f aca="false">PL!G170</f>
-        <v>14.5291680195783</v>
+        <v>14.6615886855159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34005,15 +34005,15 @@
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">PL!H156</f>
-        <v>218.003191158495</v>
+        <v>218.641899057174</v>
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">PL!H163</f>
-        <v>30.6465963753712</v>
+        <v>31.0528643106349</v>
       </c>
       <c r="D12" s="15" t="n">
         <f aca="false">PL!H170</f>
-        <v>8.27078560677316</v>
+        <v>8.35032603422065</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34022,15 +34022,15 @@
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">PL!I156</f>
-        <v>113.752032474281</v>
+        <v>114.083691919546</v>
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">PL!I163</f>
-        <v>17.0667267474526</v>
+        <v>17.2851381777775</v>
       </c>
       <c r="D13" s="15" t="n">
         <f aca="false">PL!I170</f>
-        <v>5.17807974881523</v>
+        <v>5.22433378017975</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34093,15 +34093,15 @@
       </c>
       <c r="B18" s="15" t="n">
         <f aca="false">PL!G72</f>
-        <v>374.522533805488</v>
+        <v>375.118375029163</v>
       </c>
       <c r="C18" s="15" t="n">
         <f aca="false">PL!G108</f>
-        <v>86.5990955810192</v>
+        <v>87.3131417363772</v>
       </c>
       <c r="D18" s="15" t="n">
         <f aca="false">PL!G144</f>
-        <v>28.614066071764</v>
+        <v>28.8129698779381</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34110,15 +34110,15 @@
       </c>
       <c r="B19" s="15" t="n">
         <f aca="false">B11*(1-$B$15)</f>
-        <v>268.384830945806</v>
+        <v>269.053307645248</v>
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">C11*(1-$B$15)</f>
-        <v>43.9587541250383</v>
+        <v>44.4824733812955</v>
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">D11*(1-$B$15)</f>
-        <v>12.4100191164657</v>
+        <v>12.5231255925892</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34127,15 +34127,15 @@
       </c>
       <c r="B20" s="15" t="n">
         <f aca="false">B12*(1-$B$15)</f>
-        <v>186.206379200918</v>
+        <v>186.751928486449</v>
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">C12*(1-$B$15)</f>
-        <v>26.176643174645</v>
+        <v>26.523654981256</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">D12*(1-$B$15)</f>
-        <v>7.06445182201308</v>
+        <v>7.13239089628252</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34144,15 +34144,15 @@
       </c>
       <c r="B21" s="15" t="n">
         <f aca="false">B13*(1-$B$15)</f>
-        <v>97.1607524698184</v>
+        <v>97.4440377928565</v>
       </c>
       <c r="C21" s="15" t="n">
         <f aca="false">C13*(1-$B$15)</f>
-        <v>14.5774627222963</v>
+        <v>14.7640177970215</v>
       </c>
       <c r="D21" s="15" t="n">
         <f aca="false">D13*(1-$B$15)</f>
-        <v>4.42283196001239</v>
+        <v>4.46233961885933</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34161,15 +34161,15 @@
       </c>
       <c r="B22" s="24" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(B16:B21,1/(1+tp_r)^{1;2;3;4;5;6})+B21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>2068.24140877828</v>
+        <v>2072.41602649949</v>
       </c>
       <c r="C22" s="24" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(C16:C21,1/(1+tp_r)^{1;2;3;4;5;6})+C21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>650.979406923338</v>
+        <v>654.01965509435</v>
       </c>
       <c r="D22" s="24" t="n">
         <f aca="false">MAX(0,SUMPRODUCT(D16:D21,1/(1+tp_r)^{1;2;3;4;5;6})+D21*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)</f>
-        <v>448.167637599796</v>
+        <v>448.845367501664</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>422</v>
@@ -34181,15 +34181,15 @@
       </c>
       <c r="B23" s="24" t="n">
         <f aca="false">B22*(1+tp_r)</f>
-        <v>2275.0655496561</v>
+        <v>2279.65762914944</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">C22*(1+tp_r)</f>
-        <v>716.077347615672</v>
+        <v>719.421620603785</v>
       </c>
       <c r="D23" s="24" t="n">
         <f aca="false">D22*(1+tp_r)</f>
-        <v>492.984401359775</v>
+        <v>493.729904251831</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34198,7 +34198,7 @@
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">tp_wA*B23+tp_wB*C23+tp_wC*D23</f>
-        <v>1139.15521897662</v>
+        <v>1142.35407989709</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>425</v>
@@ -34328,7 +34328,7 @@
       </c>
       <c r="B33" s="15" t="n">
         <f aca="false">tp_wA*(PL!F70+PL!G70)/2+tp_wB*(PL!F106+PL!G106)/2+tp_wC*(PL!F142+PL!G142)/2</f>
-        <v>513.85412638055</v>
+        <v>514.100843986954</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>447</v>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="B34" s="25" t="n">
         <f aca="false">B32*B33</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>449</v>
@@ -34352,7 +34352,7 @@
       </c>
       <c r="B35" s="15" t="n">
         <f aca="false">tp_wA*(8/12*B9+4/12*B10)+tp_wB*(8/12*C9+4/12*C10)+tp_wC*(8/12*D9+4/12*D10)</f>
-        <v>227.22088822143</v>
+        <v>227.43406009774</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>451</v>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">B44*B35</f>
-        <v>831.383370414327</v>
+        <v>832.163349554411</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>464</v>
@@ -34532,7 +34532,7 @@
       </c>
       <c r="B49" s="25" t="n">
         <f aca="false">tp_w_dcf*B24+(1-tp_w_dcf)*B34</f>
-        <v>952.858954177605</v>
+        <v>954.642410125009</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>468</v>
@@ -34544,7 +34544,7 @@
       </c>
       <c r="B50" s="24" t="n">
         <f aca="false">B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>470</v>
@@ -34568,7 +34568,7 @@
       </c>
       <c r="B52" s="14" t="n">
         <f aca="false">B49/px-1</f>
-        <v>-0.230342597370335</v>
+        <v>-0.228902037814101</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>474</v>
@@ -34580,7 +34580,7 @@
       </c>
       <c r="B53" s="14" t="n">
         <f aca="false">B50/px-1</f>
-        <v>-0.380820586432811</v>
+        <v>-0.380523298827229</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34613,15 +34613,15 @@
       </c>
       <c r="B56" s="29" t="n">
         <f aca="false">B23/px</f>
-        <v>1.83764977396033</v>
+        <v>1.84135895668881</v>
       </c>
       <c r="C56" s="29" t="n">
         <f aca="false">C23/px</f>
-        <v>0.578400642646521</v>
+        <v>0.581101928550831</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">D23/px</f>
-        <v>0.398200690903916</v>
+        <v>0.398802859584849</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>481</v>
@@ -34633,7 +34633,7 @@
       </c>
       <c r="B57" s="14" t="n">
         <f aca="false">B33/((cons_bv28+cons_bv29)/2)-1</f>
-        <v>-0.146208978349174</v>
+        <v>-0.145799046295665</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>483</v>
@@ -34645,7 +34645,7 @@
       </c>
       <c r="B58" s="14" t="n">
         <f aca="false">B35/(8/12*cons_eps28+4/12*cons_eps29)-1</f>
-        <v>-0.165549437306536</v>
+        <v>-0.16476658061792</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>485</v>
@@ -34670,7 +34670,7 @@
       </c>
       <c r="B60" s="28" t="str">
         <f aca="false">TEXT(D23,"#,##0")&amp;"～"&amp;TEXT(B23,"#,##0")</f>
-        <v>493～2,275</v>
+        <v>494～2,280</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>488</v>
@@ -36745,11 +36745,11 @@
       </c>
       <c r="Q62" s="13" t="n">
         <f aca="false">Units!S4*1*0.8</f>
-        <v>12.2957226040675</v>
+        <v>12.3232370004642</v>
       </c>
       <c r="R62" s="13" t="n">
         <f aca="false">Units!T4*1*0.8</f>
-        <v>12.5232673989249</v>
+        <v>12.562801359407</v>
       </c>
       <c r="T62" s="8" t="s">
         <v>358</v>
@@ -36820,11 +36820,11 @@
       </c>
       <c r="Q63" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R63" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36892,11 +36892,11 @@
       </c>
       <c r="Q64" s="13" t="n">
         <f aca="false">Q62*sd_k</f>
-        <v>12.2884398463553</v>
+        <v>12.3159379459724</v>
       </c>
       <c r="R64" s="13" t="n">
         <f aca="false">R62*sd_k</f>
-        <v>12.5158498664082</v>
+        <v>12.5553604109217</v>
       </c>
       <c r="T64" s="5" t="s">
         <v>360</v>
@@ -37039,11 +37039,11 @@
       </c>
       <c r="Q66" s="13" t="n">
         <f aca="false">Q63*Q65</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R66" s="13" t="n">
         <f aca="false">R63*R65</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37111,7 +37111,7 @@
       </c>
       <c r="Q67" s="14" t="n">
         <f aca="false">1-Q66/Q64</f>
-        <v>0.837621575533522</v>
+        <v>0.837621575533523</v>
       </c>
       <c r="R67" s="14" t="n">
         <f aca="false">1-R66/R64</f>
@@ -37183,11 +37183,11 @@
       </c>
       <c r="Q68" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q64</f>
-        <v>0.742819576484207</v>
+        <v>0.743094557480378</v>
       </c>
       <c r="R68" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R64</f>
-        <v>0.760042600820037</v>
+        <v>0.760437706265172</v>
       </c>
       <c r="T68" s="5" t="s">
         <v>365</v>
@@ -37258,11 +37258,11 @@
       </c>
       <c r="Q69" s="13" t="n">
         <f aca="false">Q64-Q66-Q68</f>
-        <v>9.55024276846887</v>
+        <v>9.57300078899809</v>
       </c>
       <c r="R69" s="13" t="n">
         <f aca="false">R64-R66-R68</f>
-        <v>9.73817717311604</v>
+        <v>9.77092327534898</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37330,11 +37330,11 @@
       </c>
       <c r="Q71" s="13" t="n">
         <f aca="false">(Q69+rf*$F87/4)*(1-tax)</f>
-        <v>8.40356464091928</v>
+        <v>8.42290895836912</v>
       </c>
       <c r="R71" s="13" t="n">
         <f aca="false">(R69+rf*$F87/4)*(1-tax)</f>
-        <v>8.56330888486938</v>
+        <v>8.59114307176737</v>
       </c>
       <c r="T71" s="5" t="s">
         <v>366</v>
@@ -37389,11 +37389,11 @@
       </c>
       <c r="Q72" s="15" t="n">
         <f aca="false">Q71/(sh0+dil)*1000</f>
-        <v>54.216546070447</v>
+        <v>54.3413481185105</v>
       </c>
       <c r="R72" s="15" t="n">
         <f aca="false">R71/(sh0+dil)*1000</f>
-        <v>55.2471540959315</v>
+        <v>55.4267294952734</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37459,7 +37459,7 @@
       </c>
       <c r="G75" s="13" t="n">
         <f aca="false">SUM(O64:R64)</f>
-        <v>49.1231872049772</v>
+        <v>49.1901958491077</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37483,7 +37483,7 @@
       </c>
       <c r="G76" s="13" t="n">
         <f aca="false">SUM(O66:R66)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37507,7 +37507,7 @@
       </c>
       <c r="G77" s="14" t="n">
         <f aca="false">1-G76/G75</f>
-        <v>0.837880806603955</v>
+        <v>0.83788139518486</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37531,7 +37531,7 @@
       </c>
       <c r="G78" s="13" t="n">
         <f aca="false">SUM(O68:R68)</f>
-        <v>2.94247439213886</v>
+        <v>2.94314447858017</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37555,7 +37555,7 @@
       </c>
       <c r="G79" s="13" t="n">
         <f aca="false">SUM(O69:R69)</f>
-        <v>38.2169013261246</v>
+        <v>38.2724054488867</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37579,7 +37579,7 @@
       </c>
       <c r="G80" s="14" t="n">
         <f aca="false">G79/G75</f>
-        <v>0.777980898646828</v>
+        <v>0.77804946266708</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37607,7 +37607,7 @@
       </c>
       <c r="G81" s="13" t="n">
         <f aca="false">SUM(O71:R71)</f>
-        <v>33.6277992780888</v>
+        <v>33.6749777824367</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37654,7 +37654,7 @@
       </c>
       <c r="G83" s="13" t="n">
         <f aca="false">cap_r*G75</f>
-        <v>2.94739123229863</v>
+        <v>2.95141175094646</v>
       </c>
       <c r="T83" s="8" t="s">
         <v>371</v>
@@ -37681,7 +37681,7 @@
       </c>
       <c r="G84" s="13" t="n">
         <f aca="false">G81+G82-G83</f>
-        <v>30.8404080457902</v>
+        <v>30.8835660314902</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37704,7 +37704,7 @@
       </c>
       <c r="G85" s="13" t="n">
         <f aca="false">MAX(0,payout*G84)</f>
-        <v>15.4202040228951</v>
+        <v>15.4417830157451</v>
       </c>
       <c r="T85" s="8" t="s">
         <v>374</v>
@@ -37731,7 +37731,7 @@
       </c>
       <c r="G86" s="13" t="n">
         <f aca="false">F86+G81-G85</f>
-        <v>68.0582866258293</v>
+        <v>68.0838861373272</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37755,7 +37755,7 @@
       </c>
       <c r="G87" s="13" t="n">
         <f aca="false">F87+G84-G85</f>
-        <v>49.0505908135707</v>
+        <v>49.0721698064207</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37779,7 +37779,7 @@
       </c>
       <c r="G88" s="20" t="n">
         <f aca="false">F88-G85/bb_px*1000</f>
-        <v>110.646560896286</v>
+        <v>110.629130791321</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37807,7 +37807,7 @@
       </c>
       <c r="G89" s="15" t="n">
         <f aca="false">G81/(G88+dil)*1000</f>
-        <v>282.049561987628</v>
+        <v>282.48656423295</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37831,7 +37831,7 @@
       </c>
       <c r="G90" s="15" t="n">
         <f aca="false">G86/G88*1000</f>
-        <v>615.096267561567</v>
+        <v>615.424578050362</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37855,7 +37855,7 @@
       </c>
       <c r="G91" s="21" t="n">
         <f aca="false">G81/G86</f>
-        <v>0.494102936545665</v>
+        <v>0.494610100758839</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="G92" s="15" t="n">
         <f aca="false">G84/(G88+dil)*1000</f>
-        <v>258.670616798365</v>
+        <v>259.0704741028</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38020,11 +38020,11 @@
       </c>
       <c r="Q112" s="13" t="n">
         <f aca="false">Units!S4*1*1.2</f>
-        <v>18.4435839061013</v>
+        <v>18.4848555006964</v>
       </c>
       <c r="R112" s="13" t="n">
         <f aca="false">Units!T4*1*1.2</f>
-        <v>18.7849010983873</v>
+        <v>18.8442020391106</v>
       </c>
       <c r="T112" s="8" t="s">
         <v>358</v>
@@ -38095,11 +38095,11 @@
       </c>
       <c r="Q113" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R113" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38167,11 +38167,11 @@
       </c>
       <c r="Q114" s="13" t="n">
         <f aca="false">Q112*sd_k</f>
-        <v>18.432659769533</v>
+        <v>18.4739069189585</v>
       </c>
       <c r="R114" s="13" t="n">
         <f aca="false">R112*sd_k</f>
-        <v>18.7737747996124</v>
+        <v>18.8330406163826</v>
       </c>
       <c r="T114" s="5" t="s">
         <v>360</v>
@@ -38314,11 +38314,11 @@
       </c>
       <c r="Q116" s="13" t="n">
         <f aca="false">Q113*Q115</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R116" s="13" t="n">
         <f aca="false">R113*R115</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38386,7 +38386,7 @@
       </c>
       <c r="Q117" s="14" t="n">
         <f aca="false">1-Q116/Q114</f>
-        <v>0.891747717022348</v>
+        <v>0.891747717022349</v>
       </c>
       <c r="R117" s="14" t="n">
         <f aca="false">1-R116/R114</f>
@@ -38458,11 +38458,11 @@
       </c>
       <c r="Q118" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q114</f>
-        <v>0.804261775715984</v>
+        <v>0.804674247210239</v>
       </c>
       <c r="R118" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R114</f>
-        <v>0.822621850152078</v>
+        <v>0.82321450831978</v>
       </c>
       <c r="T118" s="5" t="s">
         <v>365</v>
@@ -38533,11 +38533,11 @@
       </c>
       <c r="Q119" s="13" t="n">
         <f aca="false">Q114-Q116-Q118</f>
-        <v>15.6330204924148</v>
+        <v>15.6693900722544</v>
       </c>
       <c r="R119" s="13" t="n">
         <f aca="false">R114-R116-R118</f>
-        <v>15.9335228569881</v>
+        <v>15.9858266787552</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38605,11 +38605,11 @@
       </c>
       <c r="Q121" s="13" t="n">
         <f aca="false">(Q119+rf*$F137/4)*(1-tax)</f>
-        <v>13.711430214824</v>
+        <v>13.7423443576877</v>
       </c>
       <c r="R121" s="13" t="n">
         <f aca="false">(R119+rf*$F137/4)*(1-tax)</f>
-        <v>13.9668572247114</v>
+        <v>14.0113154732134</v>
       </c>
       <c r="T121" s="5" t="s">
         <v>366</v>
@@ -38664,11 +38664,11 @@
       </c>
       <c r="Q122" s="15" t="n">
         <f aca="false">Q121/(sh0+dil)*1000</f>
-        <v>88.460840095639</v>
+        <v>88.6602861786306</v>
       </c>
       <c r="R122" s="15" t="n">
         <f aca="false">R121/(sh0+dil)*1000</f>
-        <v>90.1087562884607</v>
+        <v>90.3955836981512</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38734,7 +38734,7 @@
       </c>
       <c r="G125" s="13" t="n">
         <f aca="false">SUM(O114:R114)</f>
-        <v>73.6847808074659</v>
+        <v>73.7852937736616</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38758,7 +38758,7 @@
       </c>
       <c r="G126" s="13" t="n">
         <f aca="false">SUM(O116:R116)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="G127" s="14" t="n">
         <f aca="false">1-G126/G125</f>
-        <v>0.89192053773597</v>
+        <v>0.89192093012324</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38806,7 +38806,7 @@
       </c>
       <c r="G128" s="13" t="n">
         <f aca="false">SUM(O118:R118)</f>
-        <v>3.18809032816375</v>
+        <v>3.1890954578257</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38830,7 +38830,7 @@
       </c>
       <c r="G129" s="13" t="n">
         <f aca="false">SUM(O119:R119)</f>
-        <v>62.5328789925883</v>
+        <v>62.621552394195</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38854,7 +38854,7 @@
       </c>
       <c r="G130" s="14" t="n">
         <f aca="false">G129/G125</f>
-        <v>0.848653932431219</v>
+        <v>0.848699641778054</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38882,7 +38882,7 @@
       </c>
       <c r="G131" s="13" t="n">
         <f aca="false">SUM(O121:R121)</f>
-        <v>54.846398328786</v>
+        <v>54.9217707201518</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38929,7 +38929,7 @@
       </c>
       <c r="G133" s="13" t="n">
         <f aca="false">cap_r*G125</f>
-        <v>4.42108684844795</v>
+        <v>4.4271176264197</v>
       </c>
       <c r="T133" s="8" t="s">
         <v>371</v>
@@ -38956,7 +38956,7 @@
       </c>
       <c r="G134" s="13" t="n">
         <f aca="false">G131+G132-G133</f>
-        <v>50.5853114803381</v>
+        <v>50.6546530937321</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="G135" s="13" t="n">
         <f aca="false">MAX(0,payout*G134)</f>
-        <v>25.292655740169</v>
+        <v>25.327326546866</v>
       </c>
       <c r="T135" s="8" t="s">
         <v>374</v>
@@ -39006,7 +39006,7 @@
       </c>
       <c r="G136" s="13" t="n">
         <f aca="false">F136+G131-G135</f>
-        <v>98.0480983029389</v>
+        <v>98.0887998876076</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39030,7 +39030,7 @@
       </c>
       <c r="G137" s="13" t="n">
         <f aca="false">F137+G134-G135</f>
-        <v>75.1000435368161</v>
+        <v>75.1347143435131</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39054,7 +39054,7 @@
       </c>
       <c r="G138" s="20" t="n">
         <f aca="false">F138-G135/bb_px*1000</f>
-        <v>89.605509610578</v>
+        <v>89.5775047910688</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39082,7 +39082,7 @@
       </c>
       <c r="G139" s="15" t="n">
         <f aca="false">G131/(G138+dil)*1000</f>
-        <v>558.599721550737</v>
+        <v>559.526964719146</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39106,7 +39106,7 @@
       </c>
       <c r="G140" s="15" t="n">
         <f aca="false">G136/G138*1000</f>
-        <v>1094.21952655648</v>
+        <v>1095.01598773476</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39130,7 +39130,7 @@
       </c>
       <c r="G141" s="21" t="n">
         <f aca="false">G131/G136</f>
-        <v>0.559382581387018</v>
+        <v>0.559918877415999</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39150,7 +39150,7 @@
       </c>
       <c r="G142" s="15" t="n">
         <f aca="false">G134/(G138+dil)*1000</f>
-        <v>515.201394594466</v>
+        <v>516.054816201288</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39295,11 +39295,11 @@
       </c>
       <c r="Q162" s="13" t="n">
         <f aca="false">Units!S4*0.9*1</f>
-        <v>13.832687929576</v>
+        <v>13.8636416255223</v>
       </c>
       <c r="R162" s="13" t="n">
         <f aca="false">Units!T4*0.9*1</f>
-        <v>14.0886758237905</v>
+        <v>14.1331515293329</v>
       </c>
       <c r="T162" s="8" t="s">
         <v>358</v>
@@ -39370,11 +39370,11 @@
       </c>
       <c r="Q163" s="13" t="n">
         <f aca="false">Units!S7*0.9</f>
-        <v>53.3617707585208</v>
+        <v>53.481179512309</v>
       </c>
       <c r="R163" s="13" t="n">
         <f aca="false">Units!T7*0.9</f>
-        <v>56.0301900508669</v>
+        <v>56.2070684364127</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39442,11 +39442,11 @@
       </c>
       <c r="Q164" s="13" t="n">
         <f aca="false">Q162*sd_k</f>
-        <v>13.8244948271498</v>
+        <v>13.8554301892189</v>
       </c>
       <c r="R164" s="13" t="n">
         <f aca="false">R162*sd_k</f>
-        <v>14.0803310997093</v>
+        <v>14.1247804622869</v>
       </c>
       <c r="T164" s="5" t="s">
         <v>360</v>
@@ -39589,11 +39589,11 @@
       </c>
       <c r="Q166" s="13" t="n">
         <f aca="false">Q163*Q165</f>
-        <v>1.79583975126204</v>
+        <v>1.7998583395445</v>
       </c>
       <c r="R166" s="13" t="n">
         <f aca="false">R163*R165</f>
-        <v>1.81586708322494</v>
+        <v>1.8215994863768</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39661,11 +39661,11 @@
       </c>
       <c r="Q167" s="14" t="n">
         <f aca="false">1-Q166/Q164</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R167" s="14" t="n">
         <f aca="false">1-R166/R164</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39733,11 +39733,11 @@
       </c>
       <c r="Q168" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q164</f>
-        <v>0.758180126292152</v>
+        <v>0.758489479912843</v>
       </c>
       <c r="R168" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R164</f>
-        <v>0.775687413153047</v>
+        <v>0.776131906778824</v>
       </c>
       <c r="T168" s="5" t="s">
         <v>365</v>
@@ -39808,11 +39808,11 @@
       </c>
       <c r="Q169" s="13" t="n">
         <f aca="false">Q164-Q166-Q168</f>
-        <v>11.2704749495956</v>
+        <v>11.2970823697616</v>
       </c>
       <c r="R169" s="13" t="n">
         <f aca="false">R164-R166-R168</f>
-        <v>11.4887766033313</v>
+        <v>11.5270490691313</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39880,11 +39880,11 @@
       </c>
       <c r="Q171" s="13" t="n">
         <f aca="false">(Q169+rf*$F187/4)*(1-tax)</f>
-        <v>9.90182756357116</v>
+        <v>9.92444387071225</v>
       </c>
       <c r="R171" s="13" t="n">
         <f aca="false">(R169+rf*$F187/4)*(1-tax)</f>
-        <v>10.0873839692465</v>
+        <v>10.1199155651765</v>
       </c>
       <c r="T171" s="5" t="s">
         <v>366</v>
@@ -39939,11 +39939,11 @@
       </c>
       <c r="Q172" s="15" t="n">
         <f aca="false">Q171/(sh0+dil)*1000</f>
-        <v>63.8827584746526</v>
+        <v>64.0286701336274</v>
       </c>
       <c r="R172" s="15" t="n">
         <f aca="false">R171/(sh0+dil)*1000</f>
-        <v>65.079896575784</v>
+        <v>65.2897778398485</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40009,7 +40009,7 @@
       </c>
       <c r="G175" s="13" t="n">
         <f aca="false">SUM(O164:R164)</f>
-        <v>55.2635856055994</v>
+        <v>55.3389703302462</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40033,7 +40033,7 @@
       </c>
       <c r="G176" s="13" t="n">
         <f aca="false">SUM(O166:R166)</f>
-        <v>7.16743033804244</v>
+        <v>7.17718132947676</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40057,7 +40057,7 @@
       </c>
       <c r="G177" s="14" t="n">
         <f aca="false">1-G176/G175</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="G178" s="13" t="n">
         <f aca="false">SUM(O168:R168)</f>
-        <v>3.00387837614508</v>
+        <v>3.00463222339155</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40105,7 +40105,7 @@
       </c>
       <c r="G179" s="13" t="n">
         <f aca="false">SUM(O169:R169)</f>
-        <v>45.0922768914119</v>
+        <v>45.1571567773779</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40129,7 +40129,7 @@
       </c>
       <c r="G180" s="14" t="n">
         <f aca="false">G179/G175</f>
-        <v>0.815949171543496</v>
+        <v>0.816010065020973</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="G181" s="13" t="n">
         <f aca="false">SUM(O171:R171)</f>
-        <v>39.6161307833598</v>
+        <v>39.6712786864309</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40204,7 +40204,7 @@
       </c>
       <c r="G183" s="13" t="n">
         <f aca="false">cap_r*G175</f>
-        <v>3.31581513633596</v>
+        <v>3.32033821981477</v>
       </c>
       <c r="T183" s="8" t="s">
         <v>371</v>
@@ -40231,7 +40231,7 @@
       </c>
       <c r="G184" s="13" t="n">
         <f aca="false">G181+G182-G183</f>
-        <v>36.4603156470238</v>
+        <v>36.5109404666161</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40254,7 +40254,7 @@
       </c>
       <c r="G185" s="13" t="n">
         <f aca="false">MAX(0,payout*G184)</f>
-        <v>18.2301578235119</v>
+        <v>18.2554702333081</v>
       </c>
       <c r="T185" s="8" t="s">
         <v>374</v>
@@ -40281,7 +40281,7 @@
       </c>
       <c r="G186" s="13" t="n">
         <f aca="false">F186+G181-G185</f>
-        <v>76.0330404561277</v>
+        <v>76.0628759494027</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40305,7 +40305,7 @@
       </c>
       <c r="G187" s="13" t="n">
         <f aca="false">F187+G184-G185</f>
-        <v>56.1035526958561</v>
+        <v>56.1288651056522</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="G188" s="20" t="n">
         <f aca="false">F188-G185/bb_px*1000</f>
-        <v>104.949637653485</v>
+        <v>104.929191937471</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40357,7 +40357,7 @@
       </c>
       <c r="G189" s="15" t="n">
         <f aca="false">G181/(G188+dil)*1000</f>
-        <v>348.949680472654</v>
+        <v>349.498379904638</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40381,7 +40381,7 @@
       </c>
       <c r="G190" s="15" t="n">
         <f aca="false">G186/G188*1000</f>
-        <v>724.471681428459</v>
+        <v>724.897185853956</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40405,7 +40405,7 @@
       </c>
       <c r="G191" s="21" t="n">
         <f aca="false">G181/G186</f>
-        <v>0.521038361029623</v>
+        <v>0.521559015370657</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40425,7 +40425,7 @@
       </c>
       <c r="G192" s="15" t="n">
         <f aca="false">G184/(G188+dil)*1000</f>
-        <v>321.152400382955</v>
+        <v>321.656245132366</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40570,11 +40570,11 @@
       </c>
       <c r="Q212" s="13" t="n">
         <f aca="false">Units!S4*1.1*1</f>
-        <v>16.9066185805928</v>
+        <v>16.9444508756383</v>
       </c>
       <c r="R212" s="13" t="n">
         <f aca="false">Units!T4*1.1*1</f>
-        <v>17.2194926735217</v>
+        <v>17.2738518691847</v>
       </c>
       <c r="T212" s="8" t="s">
         <v>358</v>
@@ -40645,11 +40645,11 @@
       </c>
       <c r="Q213" s="13" t="n">
         <f aca="false">Units!S7*1.1</f>
-        <v>65.219942038192</v>
+        <v>65.3658860705998</v>
       </c>
       <c r="R213" s="13" t="n">
         <f aca="false">Units!T7*1.1</f>
-        <v>68.4813433955039</v>
+        <v>68.6975280889489</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40717,11 +40717,11 @@
       </c>
       <c r="Q214" s="13" t="n">
         <f aca="false">Q212*sd_k</f>
-        <v>16.8966047887386</v>
+        <v>16.934414675712</v>
       </c>
       <c r="R214" s="13" t="n">
         <f aca="false">R212*sd_k</f>
-        <v>17.2092935663113</v>
+        <v>17.2636205650173</v>
       </c>
       <c r="T214" s="5" t="s">
         <v>360</v>
@@ -40864,11 +40864,11 @@
       </c>
       <c r="Q216" s="13" t="n">
         <f aca="false">Q213*Q215</f>
-        <v>2.19491525154249</v>
+        <v>2.19982685944328</v>
       </c>
       <c r="R216" s="13" t="n">
         <f aca="false">R213*R215</f>
-        <v>2.21939310171938</v>
+        <v>2.22639937223831</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40936,11 +40936,11 @@
       </c>
       <c r="Q217" s="14" t="n">
         <f aca="false">1-Q216/Q214</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R217" s="14" t="n">
         <f aca="false">1-R216/R214</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41008,11 +41008,11 @@
       </c>
       <c r="Q218" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q214</f>
-        <v>0.78890122590804</v>
+        <v>0.789279324777774</v>
       </c>
       <c r="R218" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R214</f>
-        <v>0.806977037819068</v>
+        <v>0.807520307806128</v>
       </c>
       <c r="T218" s="5" t="s">
         <v>365</v>
@@ -41083,11 +41083,11 @@
       </c>
       <c r="Q219" s="13" t="n">
         <f aca="false">Q214-Q216-Q218</f>
-        <v>13.9127883112881</v>
+        <v>13.9453084914909</v>
       </c>
       <c r="R219" s="13" t="n">
         <f aca="false">R214-R216-R218</f>
-        <v>14.1829234267729</v>
+        <v>14.2297008849729</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41155,11 +41155,11 @@
       </c>
       <c r="Q221" s="13" t="n">
         <f aca="false">(Q219+rf*$F237/4)*(1-tax)</f>
-        <v>12.2131672921722</v>
+        <v>12.2408094453446</v>
       </c>
       <c r="R221" s="13" t="n">
         <f aca="false">(R219+rf*$F237/4)*(1-tax)</f>
-        <v>12.4427821403343</v>
+        <v>12.4825429798043</v>
       </c>
       <c r="T221" s="5" t="s">
         <v>366</v>
@@ -41214,11 +41214,11 @@
       </c>
       <c r="Q222" s="15" t="n">
         <f aca="false">Q221/(sh0+dil)*1000</f>
-        <v>78.7946276914333</v>
+        <v>78.9729641635137</v>
       </c>
       <c r="R222" s="15" t="n">
         <f aca="false">R221/(sh0+dil)*1000</f>
-        <v>80.2760138086082</v>
+        <v>80.5325353535761</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41284,7 +41284,7 @@
       </c>
       <c r="G225" s="13" t="n">
         <f aca="false">SUM(O214:R214)</f>
-        <v>67.5443824068437</v>
+        <v>67.6365192925231</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41308,7 +41308,7 @@
       </c>
       <c r="G226" s="13" t="n">
         <f aca="false">SUM(O216:R216)</f>
-        <v>8.7601926353852</v>
+        <v>8.77211051380492</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41332,7 +41332,7 @@
       </c>
       <c r="G227" s="14" t="n">
         <f aca="false">1-G226/G225</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41356,7 +41356,7 @@
       </c>
       <c r="G228" s="13" t="n">
         <f aca="false">SUM(O218:R218)</f>
-        <v>3.12668634415753</v>
+        <v>3.12760771301432</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41380,7 +41380,7 @@
       </c>
       <c r="G229" s="13" t="n">
         <f aca="false">SUM(O219:R219)</f>
-        <v>55.657503427301</v>
+        <v>55.7368010657039</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41404,7 +41404,7 @@
       </c>
       <c r="G230" s="14" t="n">
         <f aca="false">G229/G225</f>
-        <v>0.824013803132526</v>
+        <v>0.824063710680412</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41432,7 +41432,7 @@
       </c>
       <c r="G231" s="13" t="n">
         <f aca="false">SUM(O221:R221)</f>
-        <v>48.8580668235151</v>
+        <v>48.9254698161576</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41479,7 +41479,7 @@
       </c>
       <c r="G233" s="13" t="n">
         <f aca="false">cap_r*G225</f>
-        <v>4.05266294441062</v>
+        <v>4.05819115755139</v>
       </c>
       <c r="T233" s="8" t="s">
         <v>371</v>
@@ -41506,7 +41506,7 @@
       </c>
       <c r="G234" s="13" t="n">
         <f aca="false">G231+G232-G233</f>
-        <v>44.9654038791045</v>
+        <v>45.0272786586062</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41529,7 +41529,7 @@
       </c>
       <c r="G235" s="13" t="n">
         <f aca="false">MAX(0,payout*G234)</f>
-        <v>22.4827019395522</v>
+        <v>22.5136393293031</v>
       </c>
       <c r="T235" s="8" t="s">
         <v>374</v>
@@ -41556,7 +41556,7 @@
       </c>
       <c r="G236" s="13" t="n">
         <f aca="false">F236+G231-G235</f>
-        <v>90.0733444726405</v>
+        <v>90.1098100755321</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41580,7 +41580,7 @@
       </c>
       <c r="G237" s="13" t="n">
         <f aca="false">F237+G234-G235</f>
-        <v>68.0470816545307</v>
+        <v>68.0780190442815</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41604,7 +41604,7 @@
       </c>
       <c r="G238" s="20" t="n">
         <f aca="false">F238-G235/bb_px*1000</f>
-        <v>95.3024328533794</v>
+        <v>95.2774436449185</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41632,7 +41632,7 @@
       </c>
       <c r="G239" s="15" t="n">
         <f aca="false">G231/(G238+dil)*1000</f>
-        <v>470.320779765274</v>
+        <v>471.08293925884</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41656,7 +41656,7 @@
       </c>
       <c r="G240" s="15" t="n">
         <f aca="false">G236/G238*1000</f>
-        <v>945.131638047648</v>
+        <v>945.76225629389</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41680,7 +41680,7 @@
       </c>
       <c r="G241" s="21" t="n">
         <f aca="false">G231/G236</f>
-        <v>0.54242536579016</v>
+        <v>0.542953866789278</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41700,7 +41700,7 @@
       </c>
       <c r="G242" s="15" t="n">
         <f aca="false">G234/(G238+dil)*1000</f>
-        <v>432.848968242485</v>
+        <v>433.548882760405</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41845,11 +41845,11 @@
       </c>
       <c r="Q262" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R262" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T262" s="8" t="s">
         <v>358</v>
@@ -41920,11 +41920,11 @@
       </c>
       <c r="Q263" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R263" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41992,11 +41992,11 @@
       </c>
       <c r="Q264" s="13" t="n">
         <f aca="false">Q262*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R264" s="13" t="n">
         <f aca="false">R262*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T264" s="5" t="s">
         <v>360</v>
@@ -42139,11 +42139,11 @@
       </c>
       <c r="Q266" s="13" t="n">
         <f aca="false">Q263*Q265</f>
-        <v>2.23555426675452</v>
+        <v>2.24055681343213</v>
       </c>
       <c r="R266" s="13" t="n">
         <f aca="false">R263*R265</f>
-        <v>2.28632363921714</v>
+        <v>2.29354119878231</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42211,7 +42211,7 @@
       </c>
       <c r="Q267" s="14" t="n">
         <f aca="false">1-Q266/Q264</f>
-        <v>0.854461311951325</v>
+        <v>0.854461311951326</v>
       </c>
       <c r="R267" s="14" t="n">
         <f aca="false">1-R266/R264</f>
@@ -42283,11 +42283,11 @@
       </c>
       <c r="Q268" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q264</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R268" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R264</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T268" s="5" t="s">
         <v>365</v>
@@ -42358,11 +42358,11 @@
       </c>
       <c r="Q269" s="13" t="n">
         <f aca="false">Q264-Q266-Q268</f>
-        <v>12.3514548650896</v>
+        <v>12.380481216688</v>
       </c>
       <c r="R269" s="13" t="n">
         <f aca="false">R264-R266-R268</f>
-        <v>12.5671564683071</v>
+        <v>12.6088332075773</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42430,11 +42430,11 @@
       </c>
       <c r="Q271" s="13" t="n">
         <f aca="false">(Q269+rf*$F287/4)*(1-tax)</f>
-        <v>10.8511452616358</v>
+        <v>10.8758176604945</v>
       </c>
       <c r="R271" s="13" t="n">
         <f aca="false">(R269+rf*$F287/4)*(1-tax)</f>
-        <v>11.0344916243707</v>
+        <v>11.0699168527504</v>
       </c>
       <c r="T271" s="5" t="s">
         <v>366</v>
@@ -42489,11 +42489,11 @@
       </c>
       <c r="Q272" s="15" t="n">
         <f aca="false">Q271/(sh0+dil)*1000</f>
-        <v>70.007388784747</v>
+        <v>70.1665655515772</v>
       </c>
       <c r="R272" s="15" t="n">
         <f aca="false">R271/(sh0+dil)*1000</f>
-        <v>71.1902685443271</v>
+        <v>71.4188184048413</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42559,7 +42559,7 @@
       </c>
       <c r="G275" s="13" t="n">
         <f aca="false">SUM(O264:R264)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42583,7 +42583,7 @@
       </c>
       <c r="G276" s="13" t="n">
         <f aca="false">SUM(O266:R266)</f>
-        <v>8.87369785624389</v>
+        <v>8.88591796248666</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42607,7 +42607,7 @@
       </c>
       <c r="G277" s="14" t="n">
         <f aca="false">1-G276/G275</f>
-        <v>0.855486610521155</v>
+        <v>0.855484731311183</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="G278" s="13" t="n">
         <f aca="false">SUM(O268:R268)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42655,7 +42655,7 @@
       </c>
       <c r="G279" s="13" t="n">
         <f aca="false">SUM(O269:R269)</f>
-        <v>49.4650037898264</v>
+        <v>49.5357068806951</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42679,7 +42679,7 @@
       </c>
       <c r="G280" s="14" t="n">
         <f aca="false">G279/G275</f>
-        <v>0.805566684155453</v>
+        <v>0.80561918529696</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42707,7 +42707,7 @@
       </c>
       <c r="G281" s="13" t="n">
         <f aca="false">SUM(O271:R271)</f>
-        <v>43.454887726591</v>
+        <v>43.5149853538294</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42754,7 +42754,7 @@
       </c>
       <c r="G283" s="13" t="n">
         <f aca="false">cap_r*G275</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T283" s="8" t="s">
         <v>371</v>
@@ -42781,7 +42781,7 @@
       </c>
       <c r="G284" s="13" t="n">
         <f aca="false">G281+G282-G283</f>
-        <v>39.9306486862177</v>
+        <v>39.9857206651463</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42804,7 +42804,7 @@
       </c>
       <c r="G285" s="13" t="n">
         <f aca="false">MAX(0,payout*G284)</f>
-        <v>19.9653243431089</v>
+        <v>19.9928603325732</v>
       </c>
       <c r="T285" s="8" t="s">
         <v>374</v>
@@ -42831,7 +42831,7 @@
       </c>
       <c r="G286" s="13" t="n">
         <f aca="false">F286+G281-G285</f>
-        <v>82.403038021671</v>
+        <v>82.4355996594451</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42855,7 +42855,7 @@
       </c>
       <c r="G287" s="13" t="n">
         <f aca="false">F287+G284-G285</f>
-        <v>61.4251627324803</v>
+        <v>61.4526987219446</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42879,7 +42879,7 @@
       </c>
       <c r="G288" s="20" t="n">
         <f aca="false">F288-G285/bb_px*1000</f>
-        <v>100.651187667116</v>
+        <v>100.62894588827</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42907,7 +42907,7 @@
       </c>
       <c r="G289" s="15" t="n">
         <f aca="false">G281/(G288+dil)*1000</f>
-        <v>397.824912963691</v>
+        <v>398.456234513506</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42931,7 +42931,7 @@
       </c>
       <c r="G290" s="15" t="n">
         <f aca="false">G286/G288*1000</f>
-        <v>818.699112564899</v>
+        <v>819.203648927958</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42955,7 +42955,7 @@
       </c>
       <c r="G291" s="21" t="n">
         <f aca="false">G281/G286</f>
-        <v>0.527345699501551</v>
+        <v>0.527866425835403</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42975,7 +42975,7 @@
       </c>
       <c r="G292" s="15" t="n">
         <f aca="false">G284/(G288+dil)*1000</f>
-        <v>365.56087633055</v>
+        <v>366.139608252011</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43120,11 +43120,11 @@
       </c>
       <c r="Q312" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R312" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T312" s="8" t="s">
         <v>358</v>
@@ -43195,11 +43195,11 @@
       </c>
       <c r="Q313" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R313" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43267,11 +43267,11 @@
       </c>
       <c r="Q314" s="13" t="n">
         <f aca="false">Q312*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R314" s="13" t="n">
         <f aca="false">R312*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T314" s="5" t="s">
         <v>360</v>
@@ -43414,11 +43414,11 @@
       </c>
       <c r="Q316" s="13" t="n">
         <f aca="false">Q313*Q315</f>
-        <v>1.77138749278274</v>
+        <v>1.77535136373347</v>
       </c>
       <c r="R316" s="13" t="n">
         <f aca="false">R313*R315</f>
-        <v>1.76994144900616</v>
+        <v>1.77552887224579</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43486,7 +43486,7 @@
       </c>
       <c r="Q317" s="14" t="n">
         <f aca="false">1-Q316/Q314</f>
-        <v>0.884679421314293</v>
+        <v>0.884679421314294</v>
       </c>
       <c r="R317" s="14" t="n">
         <f aca="false">1-R316/R314</f>
@@ -43558,11 +43558,11 @@
       </c>
       <c r="Q318" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q314</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R318" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R314</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T318" s="5" t="s">
         <v>365</v>
@@ -43633,11 +43633,11 @@
       </c>
       <c r="Q319" s="13" t="n">
         <f aca="false">Q314-Q316-Q318</f>
-        <v>12.8156216390613</v>
+        <v>12.8456866663867</v>
       </c>
       <c r="R319" s="13" t="n">
         <f aca="false">R314-R316-R318</f>
-        <v>13.0835386585181</v>
+        <v>13.1268455341139</v>
       </c>
     </row>
     <row r="321" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43705,11 +43705,11 @@
       </c>
       <c r="Q321" s="13" t="n">
         <f aca="false">(Q319+rf*$F337/4)*(1-tax)</f>
-        <v>11.2500642346988</v>
+        <v>11.2756195079253</v>
       </c>
       <c r="R321" s="13" t="n">
         <f aca="false">(R319+rf*$F337/4)*(1-tax)</f>
-        <v>11.477793701237</v>
+        <v>11.5146045454934</v>
       </c>
       <c r="T321" s="5" t="s">
         <v>366</v>
@@ -43764,11 +43764,11 @@
       </c>
       <c r="Q322" s="15" t="n">
         <f aca="false">Q321/(sh0+dil)*1000</f>
-        <v>72.5810595787017</v>
+        <v>72.7459323091955</v>
       </c>
       <c r="R322" s="15" t="n">
         <f aca="false">R321/(sh0+dil)*1000</f>
-        <v>74.0502819434646</v>
+        <v>74.2877712612479</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43834,7 +43834,7 @@
       </c>
       <c r="G325" s="13" t="n">
         <f aca="false">SUM(O314:R314)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G326" s="13" t="n">
         <f aca="false">SUM(O316:R316)</f>
-        <v>7.11171372986264</v>
+        <v>7.121265024053</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43882,7 +43882,7 @@
       </c>
       <c r="G327" s="14" t="n">
         <f aca="false">1-G326/G325</f>
-        <v>0.884181558493956</v>
+        <v>0.884183993966641</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43906,7 +43906,7 @@
       </c>
       <c r="G328" s="13" t="n">
         <f aca="false">SUM(O318:R318)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43930,7 +43930,7 @@
       </c>
       <c r="G329" s="13" t="n">
         <f aca="false">SUM(O319:R319)</f>
-        <v>51.2269879162076</v>
+        <v>51.3003598191287</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43954,7 +43954,7 @@
       </c>
       <c r="G330" s="14" t="n">
         <f aca="false">G329/G325</f>
-        <v>0.834261632128254</v>
+        <v>0.834318447952417</v>
       </c>
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43982,7 +43982,7 @@
       </c>
       <c r="G331" s="13" t="n">
         <f aca="false">SUM(O321:R321)</f>
-        <v>44.970083094763</v>
+        <v>45.032449212246</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44029,7 +44029,7 @@
       </c>
       <c r="G333" s="13" t="n">
         <f aca="false">cap_r*G325</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T333" s="8" t="s">
         <v>371</v>
@@ -44056,7 +44056,7 @@
       </c>
       <c r="G334" s="13" t="n">
         <f aca="false">G331+G332-G333</f>
-        <v>41.4458440543897</v>
+        <v>41.5031845235629</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44079,7 +44079,7 @@
       </c>
       <c r="G335" s="13" t="n">
         <f aca="false">MAX(0,payout*G334)</f>
-        <v>20.7229220271949</v>
+        <v>20.7515922617814</v>
       </c>
       <c r="T335" s="8" t="s">
         <v>374</v>
@@ -44106,7 +44106,7 @@
       </c>
       <c r="G336" s="13" t="n">
         <f aca="false">F336+G331-G335</f>
-        <v>83.6756021983428</v>
+        <v>83.7092980812391</v>
       </c>
     </row>
     <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44130,7 +44130,7 @@
       </c>
       <c r="G337" s="13" t="n">
         <f aca="false">F337+G334-G335</f>
-        <v>62.6977269091521</v>
+        <v>62.7263971437386</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="G338" s="20" t="n">
         <f aca="false">F338-G335/bb_px*1000</f>
-        <v>99.6232932084424</v>
+        <v>99.6001352602614</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44182,7 +44182,7 @@
       </c>
       <c r="G339" s="15" t="n">
         <f aca="false">G331/(G338+dil)*1000</f>
-        <v>415.607342080918</v>
+        <v>416.272812969833</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44206,7 +44206,7 @@
       </c>
       <c r="G340" s="15" t="n">
         <f aca="false">G336/G338*1000</f>
-        <v>839.920057885135</v>
+        <v>840.453658647165</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44230,7 +44230,7 @@
       </c>
       <c r="G341" s="21" t="n">
         <f aca="false">G331/G336</f>
-        <v>0.53743363553174</v>
+        <v>0.537962332076209</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44250,7 +44250,7 @@
       </c>
       <c r="G342" s="15" t="n">
         <f aca="false">G334/(G338+dil)*1000</f>
-        <v>383.036808080773</v>
+        <v>383.648850352367</v>
       </c>
     </row>
     <row r="343" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44395,11 +44395,11 @@
       </c>
       <c r="Q362" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R362" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T362" s="8" t="s">
         <v>358</v>
@@ -44470,11 +44470,11 @@
       </c>
       <c r="Q363" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R363" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44542,11 +44542,11 @@
       </c>
       <c r="Q364" s="13" t="n">
         <f aca="false">Q362*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R364" s="13" t="n">
         <f aca="false">R362*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T364" s="5" t="s">
         <v>360</v>
@@ -44689,11 +44689,11 @@
       </c>
       <c r="Q366" s="13" t="n">
         <f aca="false">Q363*Q365</f>
-        <v>2.12008859523991</v>
+        <v>2.12483276196226</v>
       </c>
       <c r="R366" s="13" t="n">
         <f aca="false">R363*R365</f>
-        <v>2.14373197325167</v>
+        <v>2.15049939363928</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44761,7 +44761,7 @@
       </c>
       <c r="Q367" s="14" t="n">
         <f aca="false">1-Q366/Q364</f>
-        <v>0.861978339203494</v>
+        <v>0.861978339203495</v>
       </c>
       <c r="R367" s="14" t="n">
         <f aca="false">1-R366/R364</f>
@@ -44833,11 +44833,11 @@
       </c>
       <c r="Q368" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q364</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R368" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R364</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T368" s="5" t="s">
         <v>365</v>
@@ -44908,11 +44908,11 @@
       </c>
       <c r="Q369" s="13" t="n">
         <f aca="false">Q364-Q366-Q368</f>
-        <v>12.4669205366042</v>
+        <v>12.4962052681579</v>
       </c>
       <c r="R369" s="13" t="n">
         <f aca="false">R364-R366-R368</f>
-        <v>12.7097481342726</v>
+        <v>12.7518750127204</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44980,11 +44980,11 @@
       </c>
       <c r="Q371" s="13" t="n">
         <f aca="false">(Q369+rf*$F387/4)*(1-tax)</f>
-        <v>10.9482099127031</v>
+        <v>10.9731019345237</v>
       </c>
       <c r="R371" s="13" t="n">
         <f aca="false">(R369+rf*$F387/4)*(1-tax)</f>
-        <v>11.1546133707212</v>
+        <v>11.1904212174018</v>
       </c>
       <c r="T371" s="5" t="s">
         <v>366</v>
@@ -45039,11 +45039,11 @@
       </c>
       <c r="Q372" s="15" t="n">
         <f aca="false">Q371/(sh0+dil)*1000</f>
-        <v>70.6336123400197</v>
+        <v>70.7942060291852</v>
       </c>
       <c r="R372" s="15" t="n">
         <f aca="false">R371/(sh0+dil)*1000</f>
-        <v>71.96524755304</v>
+        <v>72.1962659187215</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45109,7 +45109,7 @@
       </c>
       <c r="G375" s="13" t="n">
         <f aca="false">SUM(O364:R364)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45133,7 +45133,7 @@
       </c>
       <c r="G376" s="13" t="n">
         <f aca="false">SUM(O366:R366)</f>
-        <v>8.46154970463344</v>
+        <v>8.47306129174339</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45157,7 +45157,7 @@
       </c>
       <c r="G377" s="14" t="n">
         <f aca="false">1-G376/G375</f>
-        <v>0.862198685613362</v>
+        <v>0.862199185907131</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45181,7 +45181,7 @@
       </c>
       <c r="G378" s="13" t="n">
         <f aca="false">SUM(O368:R368)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="G379" s="13" t="n">
         <f aca="false">SUM(O369:R369)</f>
-        <v>49.8771519414368</v>
+        <v>49.9485635514383</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45229,7 +45229,7 @@
       </c>
       <c r="G380" s="14" t="n">
         <f aca="false">G379/G375</f>
-        <v>0.81227875924766</v>
+        <v>0.812333639892907</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45257,7 +45257,7 @@
       </c>
       <c r="G381" s="13" t="n">
         <f aca="false">SUM(O371:R371)</f>
-        <v>43.8008889765793</v>
+        <v>43.8615888450806</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45304,7 +45304,7 @@
       </c>
       <c r="G383" s="13" t="n">
         <f aca="false">cap_r*G375</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T383" s="8" t="s">
         <v>371</v>
@@ -45331,7 +45331,7 @@
       </c>
       <c r="G384" s="13" t="n">
         <f aca="false">G381+G382-G383</f>
-        <v>40.276649936206</v>
+        <v>40.3323241563975</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45354,7 +45354,7 @@
       </c>
       <c r="G385" s="13" t="n">
         <f aca="false">MAX(0,payout*G384)</f>
-        <v>20.138324968103</v>
+        <v>20.1661620781988</v>
       </c>
       <c r="T385" s="8" t="s">
         <v>374</v>
@@ -45381,7 +45381,7 @@
       </c>
       <c r="G386" s="13" t="n">
         <f aca="false">F386+G381-G385</f>
-        <v>82.4488422090008</v>
+        <v>82.4817049674063</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45405,7 +45405,7 @@
       </c>
       <c r="G387" s="13" t="n">
         <f aca="false">F387+G384-G385</f>
-        <v>61.4709669198101</v>
+        <v>61.4988040299058</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45429,7 +45429,7 @@
       </c>
       <c r="G388" s="20" t="n">
         <f aca="false">F388-G385/bb_px*1000</f>
-        <v>100.614190027859</v>
+        <v>100.591705023379</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45457,7 +45457,7 @@
       </c>
       <c r="G389" s="15" t="n">
         <f aca="false">G381/(G388+dil)*1000</f>
-        <v>401.128383894825</v>
+        <v>401.767003965795</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45481,7 +45481,7 @@
       </c>
       <c r="G390" s="15" t="n">
         <f aca="false">G386/G388*1000</f>
-        <v>819.455408687103</v>
+        <v>819.965273958088</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45505,7 +45505,7 @@
       </c>
       <c r="G391" s="21" t="n">
         <f aca="false">G381/G386</f>
-        <v>0.531249291112516</v>
+        <v>0.531773547387425</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45525,7 +45525,7 @@
       </c>
       <c r="G392" s="15" t="n">
         <f aca="false">G384/(G388+dil)*1000</f>
-        <v>368.853415423753</v>
+        <v>369.439353793736</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45670,11 +45670,11 @@
       </c>
       <c r="Q412" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R412" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T412" s="8" t="s">
         <v>358</v>
@@ -45745,11 +45745,11 @@
       </c>
       <c r="Q413" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R413" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45817,11 +45817,11 @@
       </c>
       <c r="Q414" s="13" t="n">
         <f aca="false">Q412*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R414" s="13" t="n">
         <f aca="false">R412*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T414" s="5" t="s">
         <v>360</v>
@@ -45964,11 +45964,11 @@
       </c>
       <c r="Q416" s="13" t="n">
         <f aca="false">Q413*Q415</f>
-        <v>1.88313751694839</v>
+        <v>1.88735145327236</v>
       </c>
       <c r="R416" s="13" t="n">
         <f aca="false">R413*R415</f>
-        <v>1.9041383997706</v>
+        <v>1.91014946140901</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46036,7 +46036,7 @@
       </c>
       <c r="Q417" s="14" t="n">
         <f aca="false">1-Q416/Q414</f>
-        <v>0.877404289527809</v>
+        <v>0.87740428952781</v>
       </c>
       <c r="R417" s="14" t="n">
         <f aca="false">1-R416/R414</f>
@@ -46108,11 +46108,11 @@
       </c>
       <c r="Q418" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q414</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R418" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R414</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T418" s="5" t="s">
         <v>365</v>
@@ -46183,11 +46183,11 @@
       </c>
       <c r="Q419" s="13" t="n">
         <f aca="false">Q414-Q416-Q418</f>
-        <v>12.7038716148957</v>
+        <v>12.7336865768478</v>
       </c>
       <c r="R419" s="13" t="n">
         <f aca="false">R414-R416-R418</f>
-        <v>12.9493417077536</v>
+        <v>12.9922249449507</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46255,11 +46255,11 @@
       </c>
       <c r="Q421" s="13" t="n">
         <f aca="false">(Q419+rf*$F437/4)*(1-tax)</f>
-        <v>11.1558561915234</v>
+        <v>11.1811989091827</v>
       </c>
       <c r="R421" s="13" t="n">
         <f aca="false">(R419+rf*$F437/4)*(1-tax)</f>
-        <v>11.3645057704527</v>
+        <v>11.4009565220701</v>
       </c>
       <c r="T421" s="5" t="s">
         <v>366</v>
@@ -46314,11 +46314,11 @@
       </c>
       <c r="Q422" s="15" t="n">
         <f aca="false">Q421/(sh0+dil)*1000</f>
-        <v>71.9732657517639</v>
+        <v>72.1367671560173</v>
       </c>
       <c r="R422" s="15" t="n">
         <f aca="false">R421/(sh0+dil)*1000</f>
-        <v>73.3193920674366</v>
+        <v>73.554558206904</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46384,7 +46384,7 @@
       </c>
       <c r="G425" s="13" t="n">
         <f aca="false">SUM(O414:R414)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="G426" s="13" t="n">
         <f aca="false">SUM(O416:R416)</f>
-        <v>7.51584709058617</v>
+        <v>7.52607208854854</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46432,7 +46432,7 @@
       </c>
       <c r="G427" s="14" t="n">
         <f aca="false">1-G426/G425</f>
-        <v>0.877600008985986</v>
+        <v>0.877600453364569</v>
       </c>
     </row>
     <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46456,7 +46456,7 @@
       </c>
       <c r="G428" s="13" t="n">
         <f aca="false">SUM(O418:R418)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46480,7 +46480,7 @@
       </c>
       <c r="G429" s="13" t="n">
         <f aca="false">SUM(O419:R419)</f>
-        <v>50.8228545554841</v>
+        <v>50.8955527546332</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46504,7 +46504,7 @@
       </c>
       <c r="G430" s="14" t="n">
         <f aca="false">G429/G425</f>
-        <v>0.827680082620285</v>
+        <v>0.827734907350346</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46532,7 +46532,7 @@
       </c>
       <c r="G431" s="13" t="n">
         <f aca="false">SUM(O421:R421)</f>
-        <v>44.6296876476098</v>
+        <v>44.6914811168865</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="G433" s="13" t="n">
         <f aca="false">cap_r*G425</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T433" s="8" t="s">
         <v>371</v>
@@ -46606,7 +46606,7 @@
       </c>
       <c r="G434" s="13" t="n">
         <f aca="false">G431+G432-G433</f>
-        <v>41.1054486072365</v>
+        <v>41.1622164282034</v>
       </c>
     </row>
     <row r="435" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46629,7 +46629,7 @@
       </c>
       <c r="G435" s="13" t="n">
         <f aca="false">MAX(0,payout*G434)</f>
-        <v>20.5527243036182</v>
+        <v>20.5811082141017</v>
       </c>
       <c r="T435" s="8" t="s">
         <v>374</v>
@@ -46656,7 +46656,7 @@
       </c>
       <c r="G436" s="13" t="n">
         <f aca="false">F436+G431-G435</f>
-        <v>83.5971076942291</v>
+        <v>83.6305172530223</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46680,7 +46680,7 @@
       </c>
       <c r="G437" s="13" t="n">
         <f aca="false">F437+G434-G435</f>
-        <v>62.6192324050384</v>
+        <v>62.6476163155218</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46704,7 +46704,7 @@
       </c>
       <c r="G438" s="20" t="n">
         <f aca="false">F438-G435/bb_px*1000</f>
-        <v>99.6866959564483</v>
+        <v>99.6637692822292</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46732,7 +46732,7 @@
       </c>
       <c r="G439" s="15" t="n">
         <f aca="false">G431/(G438+dil)*1000</f>
-        <v>412.21990985633</v>
+        <v>412.87809370681</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46756,7 +46756,7 @@
       </c>
       <c r="G440" s="15" t="n">
         <f aca="false">G436/G438*1000</f>
-        <v>838.598439763231</v>
+        <v>839.126573832426</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46780,7 +46780,7 @@
       </c>
       <c r="G441" s="21" t="n">
         <f aca="false">G431/G436</f>
-        <v>0.533866408522775</v>
+        <v>0.534392020817872</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46800,7 +46800,7 @@
       </c>
       <c r="G442" s="15" t="n">
         <f aca="false">G434/(G438+dil)*1000</f>
-        <v>379.668449693631</v>
+        <v>380.2733099665</v>
       </c>
     </row>
     <row r="443" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46945,11 +46945,11 @@
       </c>
       <c r="Q462" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R462" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T462" s="8" t="s">
         <v>358</v>
@@ -47020,11 +47020,11 @@
       </c>
       <c r="Q463" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R463" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="464" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47092,11 +47092,11 @@
       </c>
       <c r="Q464" s="13" t="n">
         <f aca="false">Q462*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R464" s="13" t="n">
         <f aca="false">R462*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T464" s="5" t="s">
         <v>360</v>
@@ -47239,11 +47239,11 @@
       </c>
       <c r="Q466" s="13" t="n">
         <f aca="false">Q463*Q465</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R466" s="13" t="n">
         <f aca="false">R463*R465</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47311,11 +47311,11 @@
       </c>
       <c r="Q467" s="14" t="n">
         <f aca="false">1-Q466/Q464</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R467" s="14" t="n">
         <f aca="false">1-R466/R464</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="468" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47383,11 +47383,11 @@
       </c>
       <c r="Q468" s="13" t="n">
         <f aca="false">(g_ox-ox_var_hi*g_rev)*(1+ox_g)^(10/4)+ox_var_hi*Q464</f>
-        <v>0.793260480666377</v>
+        <v>0.793947933156802</v>
       </c>
       <c r="R468" s="13" t="n">
         <f aca="false">(g_ox-ox_var_hi*g_rev)*(1+ox_g)^(11/4)+ox_var_hi*R464</f>
-        <v>0.810666177316768</v>
+        <v>0.811653940929605</v>
       </c>
       <c r="T468" s="5" t="s">
         <v>365</v>
@@ -47458,11 +47458,11 @@
       </c>
       <c r="Q469" s="13" t="n">
         <f aca="false">Q464-Q466-Q468</f>
-        <v>12.5719118258755</v>
+        <v>12.6011318998148</v>
       </c>
       <c r="R469" s="13" t="n">
         <f aca="false">R464-R466-R468</f>
-        <v>12.8165160632214</v>
+        <v>12.858547143415</v>
       </c>
     </row>
     <row r="471" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47530,11 +47530,11 @@
       </c>
       <c r="Q471" s="13" t="n">
         <f aca="false">(Q469+rf*$F487/4)*(1-tax)</f>
-        <v>11.0399550187029</v>
+        <v>11.0647920815513</v>
       </c>
       <c r="R471" s="13" t="n">
         <f aca="false">(R469+rf*$F487/4)*(1-tax)</f>
-        <v>11.2478686204469</v>
+        <v>11.2835950386114</v>
       </c>
       <c r="T471" s="5" t="s">
         <v>366</v>
@@ -47589,11 +47589,11 @@
       </c>
       <c r="Q472" s="15" t="n">
         <f aca="false">Q471/(sh0+dil)*1000</f>
-        <v>71.2255162496962</v>
+        <v>71.3857553648468</v>
       </c>
       <c r="R472" s="15" t="n">
         <f aca="false">R471/(sh0+dil)*1000</f>
-        <v>72.5668943254637</v>
+        <v>72.7973873458802</v>
       </c>
     </row>
     <row r="474" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47659,7 +47659,7 @@
       </c>
       <c r="G475" s="13" t="n">
         <f aca="false">SUM(O464:R464)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47683,7 +47683,7 @@
       </c>
       <c r="G476" s="13" t="n">
         <f aca="false">SUM(O466:R466)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47707,7 +47707,7 @@
       </c>
       <c r="G477" s="14" t="n">
         <f aca="false">1-G476/G475</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47731,7 +47731,7 @@
       </c>
       <c r="G478" s="13" t="n">
         <f aca="false">SUM(O468:R468)</f>
-        <v>3.14993410222089</v>
+        <v>3.15160931832415</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47755,7 +47755,7 @@
       </c>
       <c r="G479" s="13" t="n">
         <f aca="false">SUM(O469:R469)</f>
-        <v>50.2902384172868</v>
+        <v>50.3614895714197</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47779,7 +47779,7 @@
       </c>
       <c r="G480" s="14" t="n">
         <f aca="false">G479/G475</f>
-        <v>0.819006115502072</v>
+        <v>0.819049222343492</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47807,7 +47807,7 @@
       </c>
       <c r="G481" s="13" t="n">
         <f aca="false">SUM(O471:R471)</f>
-        <v>44.1620225215286</v>
+        <v>44.2225860025415</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47854,7 +47854,7 @@
       </c>
       <c r="G483" s="13" t="n">
         <f aca="false">cap_r*G475</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T483" s="8" t="s">
         <v>371</v>
@@ -47881,7 +47881,7 @@
       </c>
       <c r="G484" s="13" t="n">
         <f aca="false">G481+G482-G483</f>
-        <v>40.6377834811553</v>
+        <v>40.6933213138585</v>
       </c>
     </row>
     <row r="485" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47904,7 +47904,7 @@
       </c>
       <c r="G485" s="13" t="n">
         <f aca="false">MAX(0,payout*G484)</f>
-        <v>20.3188917405777</v>
+        <v>20.3466606569292</v>
       </c>
       <c r="T485" s="8" t="s">
         <v>374</v>
@@ -47931,7 +47931,7 @@
       </c>
       <c r="G486" s="13" t="n">
         <f aca="false">F486+G481-G485</f>
-        <v>82.9238219366751</v>
+        <v>82.9566165013364</v>
       </c>
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47955,7 +47955,7 @@
       </c>
       <c r="G487" s="13" t="n">
         <f aca="false">F487+G484-G485</f>
-        <v>61.9459466474844</v>
+        <v>61.9737155638359</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47979,7 +47979,7 @@
       </c>
       <c r="G488" s="20" t="n">
         <f aca="false">F488-G485/bb_px*1000</f>
-        <v>100.230532339697</v>
+        <v>100.208102417683</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="G489" s="15" t="n">
         <f aca="false">G481/(G488+dil)*1000</f>
-        <v>405.861653021405</v>
+        <v>406.502044063169</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48031,7 +48031,7 @@
       </c>
       <c r="G490" s="15" t="n">
         <f aca="false">G486/G488*1000</f>
-        <v>827.330953961542</v>
+        <v>827.843402877347</v>
       </c>
     </row>
     <row r="491" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48055,7 +48055,7 @@
       </c>
       <c r="G491" s="21" t="n">
         <f aca="false">G481/G486</f>
-        <v>0.532561349563133</v>
+        <v>0.533080878507492</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48075,7 +48075,7 @@
       </c>
       <c r="G492" s="15" t="n">
         <f aca="false">G484/(G488+dil)*1000</f>
-        <v>373.472885458253</v>
+        <v>374.060401914354</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48220,11 +48220,11 @@
       </c>
       <c r="Q512" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R512" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T512" s="8" t="s">
         <v>358</v>
@@ -48295,11 +48295,11 @@
       </c>
       <c r="Q513" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R513" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48367,11 +48367,11 @@
       </c>
       <c r="Q514" s="13" t="n">
         <f aca="false">Q512*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R514" s="13" t="n">
         <f aca="false">R512*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T514" s="5" t="s">
         <v>360</v>
@@ -48514,11 +48514,11 @@
       </c>
       <c r="Q516" s="13" t="n">
         <f aca="false">Q513*Q515</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R516" s="13" t="n">
         <f aca="false">R513*R515</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48586,11 +48586,11 @@
       </c>
       <c r="Q517" s="14" t="n">
         <f aca="false">1-Q516/Q514</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R517" s="14" t="n">
         <f aca="false">1-R516/R514</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48658,11 +48658,11 @@
       </c>
       <c r="Q518" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q514</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R518" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R514</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T518" s="5" t="s">
         <v>365</v>
@@ -48733,11 +48733,11 @@
       </c>
       <c r="Q519" s="13" t="n">
         <f aca="false">Q514-Q516-Q518</f>
-        <v>12.5916316304418</v>
+        <v>12.6211954306263</v>
       </c>
       <c r="R519" s="13" t="n">
         <f aca="false">R514-R516-R518</f>
-        <v>12.8358500150521</v>
+        <v>12.8783749770521</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48805,11 +48805,11 @@
       </c>
       <c r="Q521" s="13" t="n">
         <f aca="false">(Q519+rf*$F537/4)*(1-tax_hi)</f>
-        <v>10.3880004019183</v>
+        <v>10.4116514420658</v>
       </c>
       <c r="R521" s="13" t="n">
         <f aca="false">(R519+rf*$F537/4)*(1-tax_hi)</f>
-        <v>10.5833751096065</v>
+        <v>10.6173950792065</v>
       </c>
       <c r="T521" s="5" t="s">
         <v>366</v>
@@ -48864,11 +48864,11 @@
       </c>
       <c r="Q522" s="15" t="n">
         <f aca="false">Q521/(sh0+dil)*1000</f>
-        <v>67.0193574317309</v>
+        <v>67.1719447875215</v>
       </c>
       <c r="R522" s="15" t="n">
         <f aca="false">R521/(sh0+dil)*1000</f>
-        <v>68.2798394168162</v>
+        <v>68.499323091655</v>
       </c>
     </row>
     <row r="524" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48934,7 +48934,7 @@
       </c>
       <c r="G525" s="13" t="n">
         <f aca="false">SUM(O514:R514)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48958,7 +48958,7 @@
       </c>
       <c r="G526" s="13" t="n">
         <f aca="false">SUM(O516:R516)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="527" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48982,7 +48982,7 @@
       </c>
       <c r="G527" s="14" t="n">
         <f aca="false">1-G526/G525</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="528" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49006,7 +49006,7 @@
       </c>
       <c r="G528" s="13" t="n">
         <f aca="false">SUM(O518:R518)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="529" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49030,7 +49030,7 @@
       </c>
       <c r="G529" s="13" t="n">
         <f aca="false">SUM(O519:R519)</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49054,7 +49054,7 @@
       </c>
       <c r="G530" s="14" t="n">
         <f aca="false">G529/G525</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="531" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49082,7 +49082,7 @@
       </c>
       <c r="G531" s="13" t="n">
         <f aca="false">SUM(O521:R521)</f>
-        <v>41.5586925177445</v>
+        <v>41.6163635274921</v>
       </c>
     </row>
     <row r="532" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49129,7 +49129,7 @@
       </c>
       <c r="G533" s="13" t="n">
         <f aca="false">cap_r*G525</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T533" s="8" t="s">
         <v>371</v>
@@ -49156,7 +49156,7 @@
       </c>
       <c r="G534" s="13" t="n">
         <f aca="false">G531+G532-G533</f>
-        <v>38.0344534773712</v>
+        <v>38.087098838809</v>
       </c>
     </row>
     <row r="535" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49179,7 +49179,7 @@
       </c>
       <c r="G535" s="13" t="n">
         <f aca="false">MAX(0,payout*G534)</f>
-        <v>19.0172267386856</v>
+        <v>19.0435494194045</v>
       </c>
       <c r="T535" s="8" t="s">
         <v>374</v>
@@ -49206,7 +49206,7 @@
       </c>
       <c r="G536" s="13" t="n">
         <f aca="false">F536+G531-G535</f>
-        <v>79.3319892234811</v>
+        <v>79.3633375525098</v>
       </c>
     </row>
     <row r="537" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49230,7 +49230,7 @@
       </c>
       <c r="G537" s="13" t="n">
         <f aca="false">F537+G534-G535</f>
-        <v>58.3541139342904</v>
+        <v>58.3804366150093</v>
       </c>
     </row>
     <row r="538" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49254,7 +49254,7 @@
       </c>
       <c r="G538" s="20" t="n">
         <f aca="false">F538-G535/bb_px*1000</f>
-        <v>103.131780866142</v>
+        <v>103.110519119077</v>
       </c>
     </row>
     <row r="539" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49282,7 +49282,7 @@
       </c>
       <c r="G539" s="15" t="n">
         <f aca="false">G531/(G538+dil)*1000</f>
-        <v>372.017097888199</v>
+        <v>372.604262704908</v>
       </c>
     </row>
     <row r="540" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49306,7 +49306,7 @@
       </c>
       <c r="G540" s="15" t="n">
         <f aca="false">G536/G538*1000</f>
-        <v>769.229315708692</v>
+        <v>769.69195995277</v>
       </c>
     </row>
     <row r="541" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="G541" s="21" t="n">
         <f aca="false">G531/G536</f>
-        <v>0.523857940844924</v>
+        <v>0.524377688878786</v>
       </c>
     </row>
     <row r="542" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49350,7 +49350,7 @@
       </c>
       <c r="G542" s="15" t="n">
         <f aca="false">G534/(G538+dil)*1000</f>
-        <v>340.469493749686</v>
+        <v>341.005656874091</v>
       </c>
     </row>
     <row r="543" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49495,11 +49495,11 @@
       </c>
       <c r="Q562" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R562" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T562" s="8" t="s">
         <v>358</v>
@@ -49570,11 +49570,11 @@
       </c>
       <c r="Q563" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R563" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="564" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49642,11 +49642,11 @@
       </c>
       <c r="Q564" s="13" t="n">
         <f aca="false">Q562*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R564" s="13" t="n">
         <f aca="false">R562*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T564" s="5" t="s">
         <v>360</v>
@@ -49789,11 +49789,11 @@
       </c>
       <c r="Q566" s="13" t="n">
         <f aca="false">Q563*Q565</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R566" s="13" t="n">
         <f aca="false">R563*R565</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="567" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49861,11 +49861,11 @@
       </c>
       <c r="Q567" s="14" t="n">
         <f aca="false">1-Q566/Q564</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R567" s="14" t="n">
         <f aca="false">1-R566/R564</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="568" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49933,11 +49933,11 @@
       </c>
       <c r="Q568" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q564</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R568" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R564</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T568" s="5" t="s">
         <v>365</v>
@@ -50008,11 +50008,11 @@
       </c>
       <c r="Q569" s="13" t="n">
         <f aca="false">Q564-Q566-Q568</f>
-        <v>12.5916316304418</v>
+        <v>12.6211954306263</v>
       </c>
       <c r="R569" s="13" t="n">
         <f aca="false">R564-R566-R568</f>
-        <v>12.8358500150521</v>
+        <v>12.8783749770521</v>
       </c>
     </row>
     <row r="571" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50080,11 +50080,11 @@
       </c>
       <c r="Q571" s="13" t="n">
         <f aca="false">(Q569+rf*$F587/4)*(1-tax_lo)</f>
-        <v>11.4603482371625</v>
+        <v>11.4863643813248</v>
       </c>
       <c r="R571" s="13" t="n">
         <f aca="false">(R569+rf*$F587/4)*(1-tax_lo)</f>
-        <v>11.6752604156195</v>
+        <v>11.7126823821795</v>
       </c>
       <c r="T571" s="5" t="s">
         <v>366</v>
@@ -50139,11 +50139,11 @@
       </c>
       <c r="Q572" s="15" t="n">
         <f aca="false">Q571/(sh0+dil)*1000</f>
-        <v>73.9377305623386</v>
+        <v>74.1055766537083</v>
       </c>
       <c r="R572" s="15" t="n">
         <f aca="false">R571/(sh0+dil)*1000</f>
-        <v>75.3242607459324</v>
+        <v>75.5656927882551</v>
       </c>
     </row>
     <row r="574" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50209,7 +50209,7 @@
       </c>
       <c r="G575" s="13" t="n">
         <f aca="false">SUM(O564:R564)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="576" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50233,7 +50233,7 @@
       </c>
       <c r="G576" s="13" t="n">
         <f aca="false">SUM(O566:R566)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="577" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50257,7 +50257,7 @@
       </c>
       <c r="G577" s="14" t="n">
         <f aca="false">1-G576/G575</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="578" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50281,7 +50281,7 @@
       </c>
       <c r="G578" s="13" t="n">
         <f aca="false">SUM(O568:R568)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="579" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50305,7 +50305,7 @@
       </c>
       <c r="G579" s="13" t="n">
         <f aca="false">SUM(O569:R569)</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="580" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50329,7 +50329,7 @@
       </c>
       <c r="G580" s="14" t="n">
         <f aca="false">G579/G575</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="581" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50357,7 +50357,7 @@
       </c>
       <c r="G581" s="13" t="n">
         <f aca="false">SUM(O571:R571)</f>
-        <v>45.8487529497284</v>
+        <v>45.9121910604507</v>
       </c>
     </row>
     <row r="582" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50404,7 +50404,7 @@
       </c>
       <c r="G583" s="13" t="n">
         <f aca="false">cap_r*G575</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T583" s="8" t="s">
         <v>371</v>
@@ -50431,7 +50431,7 @@
       </c>
       <c r="G584" s="13" t="n">
         <f aca="false">G581+G582-G583</f>
-        <v>42.3245139093551</v>
+        <v>42.3829263717676</v>
       </c>
     </row>
     <row r="585" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50454,7 +50454,7 @@
       </c>
       <c r="G585" s="13" t="n">
         <f aca="false">MAX(0,payout*G584)</f>
-        <v>21.1622569546776</v>
+        <v>21.1914631858838</v>
       </c>
       <c r="T585" s="8" t="s">
         <v>374</v>
@@ -50481,7 +50481,7 @@
       </c>
       <c r="G586" s="13" t="n">
         <f aca="false">F586+G581-G585</f>
-        <v>85.2892688772419</v>
+        <v>85.323500756758</v>
       </c>
     </row>
     <row r="587" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50505,7 +50505,7 @@
       </c>
       <c r="G587" s="13" t="n">
         <f aca="false">F587+G584-G585</f>
-        <v>64.3113935880512</v>
+        <v>64.3405998192575</v>
       </c>
     </row>
     <row r="588" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50529,7 +50529,7 @@
       </c>
       <c r="G588" s="20" t="n">
         <f aca="false">F588-G585/bb_px*1000</f>
-        <v>98.3198783647801</v>
+        <v>98.2962874734396</v>
       </c>
     </row>
     <row r="589" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50557,7 +50557,7 @@
       </c>
       <c r="G589" s="15" t="n">
         <f aca="false">G581/(G588+dil)*1000</f>
-        <v>428.894341612591</v>
+        <v>429.582577630801</v>
       </c>
     </row>
     <row r="590" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50581,7 +50581,7 @@
       </c>
       <c r="G590" s="15" t="n">
         <f aca="false">G586/G588*1000</f>
-        <v>867.467192756353</v>
+        <v>868.02363497007</v>
       </c>
     </row>
     <row r="591" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50605,7 +50605,7 @@
       </c>
       <c r="G591" s="21" t="n">
         <f aca="false">G581/G586</f>
-        <v>0.537567663004817</v>
+        <v>0.538095491315319</v>
       </c>
     </row>
     <row r="592" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50625,7 +50625,7 @@
       </c>
       <c r="G592" s="15" t="n">
         <f aca="false">G584/(G588+dil)*1000</f>
-        <v>395.92667977534</v>
+        <v>396.560615770832</v>
       </c>
     </row>
     <row r="593" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50770,11 +50770,11 @@
       </c>
       <c r="Q612" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R612" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T612" s="8" t="s">
         <v>358</v>
@@ -50845,11 +50845,11 @@
       </c>
       <c r="Q613" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R613" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="614" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50917,11 +50917,11 @@
       </c>
       <c r="Q614" s="13" t="n">
         <f aca="false">Q612*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R614" s="13" t="n">
         <f aca="false">R612*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T614" s="5" t="s">
         <v>360</v>
@@ -51064,11 +51064,11 @@
       </c>
       <c r="Q616" s="13" t="n">
         <f aca="false">Q613*Q615</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R616" s="13" t="n">
         <f aca="false">R613*R615</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51136,11 +51136,11 @@
       </c>
       <c r="Q617" s="14" t="n">
         <f aca="false">1-Q616/Q614</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R617" s="14" t="n">
         <f aca="false">1-R616/R614</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="618" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51208,11 +51208,11 @@
       </c>
       <c r="Q618" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q614</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R618" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R614</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T618" s="5" t="s">
         <v>365</v>
@@ -51283,11 +51283,11 @@
       </c>
       <c r="Q619" s="13" t="n">
         <f aca="false">Q614-Q616-Q618</f>
-        <v>12.5916316304418</v>
+        <v>12.6211954306263</v>
       </c>
       <c r="R619" s="13" t="n">
         <f aca="false">R614-R616-R618</f>
-        <v>12.8358500150521</v>
+        <v>12.8783749770521</v>
       </c>
     </row>
     <row r="621" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51355,11 +51355,11 @@
       </c>
       <c r="Q621" s="13" t="n">
         <f aca="false">(Q619+rf*$F637/4)*(1-tax)</f>
-        <v>10.8684253037964</v>
+        <v>10.8935545339531</v>
       </c>
       <c r="R621" s="13" t="n">
         <f aca="false">(R619+rf*$F637/4)*(1-tax)</f>
-        <v>11.0760109307151</v>
+        <v>11.1121571484151</v>
       </c>
       <c r="T621" s="5" t="s">
         <v>366</v>
@@ -51414,11 +51414,11 @@
       </c>
       <c r="Q622" s="15" t="n">
         <f aca="false">Q621/(sh0+dil)*1000</f>
-        <v>70.1188729277185</v>
+        <v>70.2809969932461</v>
       </c>
       <c r="R622" s="15" t="n">
         <f aca="false">R621/(sh0+dil)*1000</f>
-        <v>71.4581350368716</v>
+        <v>71.6913364413878</v>
       </c>
     </row>
     <row r="624" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51484,7 +51484,7 @@
       </c>
       <c r="G625" s="13" t="n">
         <f aca="false">SUM(O614:R614)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="626" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51508,7 +51508,7 @@
       </c>
       <c r="G626" s="13" t="n">
         <f aca="false">SUM(O616:R616)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="627" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51532,7 +51532,7 @@
       </c>
       <c r="G627" s="14" t="n">
         <f aca="false">1-G626/G625</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="628" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51556,7 +51556,7 @@
       </c>
       <c r="G628" s="13" t="n">
         <f aca="false">SUM(O618:R618)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="629" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51580,7 +51580,7 @@
       </c>
       <c r="G629" s="13" t="n">
         <f aca="false">SUM(O619:R619)</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="630" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51604,7 +51604,7 @@
       </c>
       <c r="G630" s="14" t="n">
         <f aca="false">G629/G625</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="631" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51632,7 +51632,7 @@
       </c>
       <c r="G631" s="13" t="n">
         <f aca="false">SUM(O621:R621)</f>
-        <v>43.4808103071363</v>
+        <v>43.5420857549931</v>
       </c>
     </row>
     <row r="632" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51679,7 +51679,7 @@
       </c>
       <c r="G633" s="13" t="n">
         <f aca="false">cap_r*G625</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T633" s="8" t="s">
         <v>371</v>
@@ -51706,7 +51706,7 @@
       </c>
       <c r="G634" s="13" t="n">
         <f aca="false">G631+G632-G633</f>
-        <v>39.956571266763</v>
+        <v>40.01282106631</v>
       </c>
     </row>
     <row r="635" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51729,7 +51729,7 @@
       </c>
       <c r="G635" s="13" t="n">
         <f aca="false">MAX(0,payout_hi*G634)</f>
-        <v>31.9652570134104</v>
+        <v>32.010256853048</v>
       </c>
       <c r="T635" s="8" t="s">
         <v>374</v>
@@ -51756,7 +51756,7 @@
       </c>
       <c r="G636" s="13" t="n">
         <f aca="false">F636+G631-G635</f>
-        <v>48.4442975332288</v>
+        <v>48.460573141448</v>
       </c>
     </row>
     <row r="637" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51780,7 +51780,7 @@
       </c>
       <c r="G637" s="13" t="n">
         <f aca="false">F637+G634-G635</f>
-        <v>27.4664222440381</v>
+        <v>27.4776722039475</v>
       </c>
     </row>
     <row r="638" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51804,7 +51804,7 @@
       </c>
       <c r="G638" s="20" t="n">
         <f aca="false">F638-G635/bb_px*1000</f>
-        <v>73.0633858822869</v>
+        <v>73.0270379427074</v>
       </c>
     </row>
     <row r="639" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51832,7 +51832,7 @@
       </c>
       <c r="G639" s="15" t="n">
         <f aca="false">G631/(G638+dil)*1000</f>
-        <v>532.569905538052</v>
+        <v>533.557973094943</v>
       </c>
     </row>
     <row r="640" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51856,7 +51856,7 @@
       </c>
       <c r="G640" s="15" t="n">
         <f aca="false">G636/G638*1000</f>
-        <v>663.044792521358</v>
+        <v>663.597682538723</v>
       </c>
     </row>
     <row r="641" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51880,7 +51880,7 @@
       </c>
       <c r="G641" s="21" t="n">
         <f aca="false">G631/G636</f>
-        <v>0.897542384164246</v>
+        <v>0.898505381434538</v>
       </c>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51900,7 +51900,7 @@
       </c>
       <c r="G642" s="15" t="n">
         <f aca="false">G634/(G638+dil)*1000</f>
-        <v>489.403652665412</v>
+        <v>490.310910370269</v>
       </c>
     </row>
     <row r="643" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52045,11 +52045,11 @@
       </c>
       <c r="Q662" s="13" t="n">
         <f aca="false">Units!S4*1*1</f>
-        <v>15.3696532550844</v>
+        <v>15.4040462505803</v>
       </c>
       <c r="R662" s="13" t="n">
         <f aca="false">Units!T4*1*1</f>
-        <v>15.6540842486561</v>
+        <v>15.7035016992588</v>
       </c>
       <c r="T662" s="8" t="s">
         <v>358</v>
@@ -52120,11 +52120,11 @@
       </c>
       <c r="Q663" s="13" t="n">
         <f aca="false">Units!S7*1</f>
-        <v>59.2908563983564</v>
+        <v>59.4235327914544</v>
       </c>
       <c r="R663" s="13" t="n">
         <f aca="false">Units!T7*1</f>
-        <v>62.2557667231854</v>
+        <v>62.4522982626808</v>
       </c>
     </row>
     <row r="664" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52192,11 +52192,11 @@
       </c>
       <c r="Q664" s="13" t="n">
         <f aca="false">Q662*sd_k</f>
-        <v>15.3605498079442</v>
+        <v>15.3949224324654</v>
       </c>
       <c r="R664" s="13" t="n">
         <f aca="false">R662*sd_k</f>
-        <v>15.6448123330103</v>
+        <v>15.6942005136521</v>
       </c>
       <c r="T664" s="5" t="s">
         <v>360</v>
@@ -52339,11 +52339,11 @@
       </c>
       <c r="Q666" s="13" t="n">
         <f aca="false">Q663*Q665</f>
-        <v>1.99537750140227</v>
+        <v>1.99984259949389</v>
       </c>
       <c r="R666" s="13" t="n">
         <f aca="false">R663*R665</f>
-        <v>2.01763009247216</v>
+        <v>2.02399942930756</v>
       </c>
     </row>
     <row r="667" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52411,11 +52411,11 @@
       </c>
       <c r="Q667" s="14" t="n">
         <f aca="false">1-Q666/Q664</f>
-        <v>0.870097260426818</v>
+        <v>0.870097260426819</v>
       </c>
       <c r="R667" s="14" t="n">
         <f aca="false">1-R666/R664</f>
-        <v>0.871035200069803</v>
+        <v>0.871035200069802</v>
       </c>
     </row>
     <row r="668" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52483,11 +52483,11 @@
       </c>
       <c r="Q668" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(10/4)+ox_var*Q664</f>
-        <v>0.773540676100096</v>
+        <v>0.773884402345309</v>
       </c>
       <c r="R668" s="13" t="n">
         <f aca="false">(g_ox-ox_var*g_rev)*(1+ox_g)^(11/4)+ox_var*R664</f>
-        <v>0.791332225486057</v>
+        <v>0.791826107292476</v>
       </c>
       <c r="T668" s="5" t="s">
         <v>365</v>
@@ -52558,11 +52558,11 @@
       </c>
       <c r="Q669" s="13" t="n">
         <f aca="false">Q664-Q666-Q668</f>
-        <v>12.5916316304418</v>
+        <v>12.6211954306263</v>
       </c>
       <c r="R669" s="13" t="n">
         <f aca="false">R664-R666-R668</f>
-        <v>12.8358500150521</v>
+        <v>12.8783749770521</v>
       </c>
     </row>
     <row r="671" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52630,11 +52630,11 @@
       </c>
       <c r="Q671" s="13" t="n">
         <f aca="false">(Q669+rf*$F687/4)*(1-tax)</f>
-        <v>11.1845321753846</v>
+        <v>11.2096614055413</v>
       </c>
       <c r="R671" s="13" t="n">
         <f aca="false">(R669+rf*$F687/4)*(1-tax)</f>
-        <v>11.3921178023033</v>
+        <v>11.4282640200033</v>
       </c>
       <c r="T671" s="5" t="s">
         <v>366</v>
@@ -52689,11 +52689,11 @@
       </c>
       <c r="Q672" s="15" t="n">
         <f aca="false">Q671/(sh0+dil)*1000</f>
-        <v>72.1582720992552</v>
+        <v>72.3203961647828</v>
       </c>
       <c r="R672" s="15" t="n">
         <f aca="false">R671/(sh0+dil)*1000</f>
-        <v>73.4975342084083</v>
+        <v>73.7307356129246</v>
       </c>
     </row>
     <row r="674" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52759,7 +52759,7 @@
       </c>
       <c r="G675" s="13" t="n">
         <f aca="false">SUM(O664:R664)</f>
-        <v>61.4039840062216</v>
+        <v>61.4877448113847</v>
       </c>
     </row>
     <row r="676" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52783,7 +52783,7 @@
       </c>
       <c r="G676" s="13" t="n">
         <f aca="false">SUM(O666:R666)</f>
-        <v>7.96381148671382</v>
+        <v>7.97464592164084</v>
       </c>
     </row>
     <row r="677" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52807,7 +52807,7 @@
       </c>
       <c r="G677" s="14" t="n">
         <f aca="false">1-G676/G675</f>
-        <v>0.870304645283164</v>
+        <v>0.870305116147888</v>
       </c>
     </row>
     <row r="678" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52831,7 +52831,7 @@
       </c>
       <c r="G678" s="13" t="n">
         <f aca="false">SUM(O668:R668)</f>
-        <v>3.0652823601513</v>
+        <v>3.06611996820293</v>
       </c>
     </row>
     <row r="679" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52855,7 +52855,7 @@
       </c>
       <c r="G679" s="13" t="n">
         <f aca="false">SUM(O669:R669)</f>
-        <v>50.3748901593564</v>
+        <v>50.4469789215409</v>
       </c>
     </row>
     <row r="680" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52879,7 +52879,7 @@
       </c>
       <c r="G680" s="14" t="n">
         <f aca="false">G679/G675</f>
-        <v>0.820384718917463</v>
+        <v>0.820439570133664</v>
       </c>
     </row>
     <row r="681" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52907,7 +52907,7 @@
       </c>
       <c r="G681" s="13" t="n">
         <f aca="false">SUM(O671:R671)</f>
-        <v>44.745237793489</v>
+        <v>44.8065132413458</v>
       </c>
     </row>
     <row r="682" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52954,7 +52954,7 @@
       </c>
       <c r="G683" s="13" t="n">
         <f aca="false">cap_r*G675</f>
-        <v>3.68423904037329</v>
+        <v>3.68926468868308</v>
       </c>
       <c r="T683" s="8" t="s">
         <v>371</v>
@@ -52981,7 +52981,7 @@
       </c>
       <c r="G684" s="13" t="n">
         <f aca="false">G681+G682-G683</f>
-        <v>41.2209987531157</v>
+        <v>41.2772485526627</v>
       </c>
     </row>
     <row r="685" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53004,7 +53004,7 @@
       </c>
       <c r="G685" s="13" t="n">
         <f aca="false">MAX(0,payout_lo*G684)</f>
-        <v>12.3662996259347</v>
+        <v>12.3831745657988</v>
       </c>
       <c r="T685" s="8" t="s">
         <v>374</v>
@@ -53031,7 +53031,7 @@
       </c>
       <c r="G686" s="13" t="n">
         <f aca="false">F686+G681-G685</f>
-        <v>106.496726123315</v>
+        <v>106.541126631308</v>
       </c>
     </row>
     <row r="687" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53055,7 +53055,7 @@
       </c>
       <c r="G687" s="13" t="n">
         <f aca="false">F687+G684-G685</f>
-        <v>85.5188508341246</v>
+        <v>85.5582256938075</v>
       </c>
     </row>
     <row r="688" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53079,7 +53079,7 @@
       </c>
       <c r="G688" s="20" t="n">
         <f aca="false">F688-G685/bb_px*1000</f>
-        <v>118.464232426589</v>
+        <v>118.450601949246</v>
       </c>
     </row>
     <row r="689" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53107,7 +53107,7 @@
       </c>
       <c r="G689" s="15" t="n">
         <f aca="false">G681/(G688+dil)*1000</f>
-        <v>352.202039705696</v>
+        <v>352.722198854476</v>
       </c>
     </row>
     <row r="690" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53131,7 +53131,7 @@
       </c>
       <c r="G690" s="15" t="n">
         <f aca="false">G686/G688*1000</f>
-        <v>898.977893511533</v>
+        <v>899.456185768974</v>
       </c>
     </row>
     <row r="691" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53155,7 +53155,7 @@
       </c>
       <c r="G691" s="21" t="n">
         <f aca="false">G681/G686</f>
-        <v>0.420155993731463</v>
+        <v>0.420556029939513</v>
       </c>
     </row>
     <row r="692" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53175,7 +53175,7 @@
       </c>
       <c r="G692" s="15" t="n">
         <f aca="false">G684/(G688+dil)*1000</f>
-        <v>324.461787566271</v>
+        <v>324.939407664577</v>
       </c>
     </row>
     <row r="693" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53224,15 +53224,15 @@
       </c>
       <c r="C698" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+tp_r)^1+Val!B17/(1+tp_r)^2+Val!B18/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C16/(1+tp_r)^1+Val!C17/(1+tp_r)^2+Val!C18/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D16/(1+tp_r)^1+Val!D17/(1+tp_r)^2+Val!D18/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1139.15521897662</v>
+        <v>1142.35407989709</v>
       </c>
       <c r="D698" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E698" s="24" t="n">
         <f aca="false">tp_w_dcf*C698+(1-tp_w_dcf)*D698</f>
-        <v>952.858954177605</v>
+        <v>954.642410125009</v>
       </c>
       <c r="F698" s="14" t="n">
         <f aca="false">E698/E$698-1</f>
@@ -53248,19 +53248,19 @@
       </c>
       <c r="C699" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+(tp_r+0.01))^1+Val!B17/(1+(tp_r+0.01))^2+Val!B18/(1+(tp_r+0.01))^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*MAX(0,Val!C16/(1+(tp_r+0.01))^1+Val!C17/(1+(tp_r+0.01))^2+Val!C18/(1+(tp_r+0.01))^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*MAX(0,Val!D16/(1+(tp_r+0.01))^1+Val!D17/(1+(tp_r+0.01))^2+Val!D18/(1+(tp_r+0.01))^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
-        <v>1057.40580166397</v>
+        <v>1060.21052868601</v>
       </c>
       <c r="D699" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E699" s="24" t="n">
         <f aca="false">tp_w_dcf*C699+(1-tp_w_dcf)*D699</f>
-        <v>911.984245521279</v>
+        <v>913.570634519466</v>
       </c>
       <c r="F699" s="14" t="n">
         <f aca="false">E699/E$698-1</f>
-        <v>-0.0428969140470574</v>
+        <v>-0.0430232044689538</v>
       </c>
     </row>
     <row r="700" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53272,19 +53272,19 @@
       </c>
       <c r="C700" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+(tp_r-0.01))^1+Val!B17/(1+(tp_r-0.01))^2+Val!B18/(1+(tp_r-0.01))^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*MAX(0,Val!C16/(1+(tp_r-0.01))^1+Val!C17/(1+(tp_r-0.01))^2+Val!C18/(1+(tp_r-0.01))^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*MAX(0,Val!D16/(1+(tp_r-0.01))^1+Val!D17/(1+(tp_r-0.01))^2+Val!D18/(1+(tp_r-0.01))^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
-        <v>1251.4620602165</v>
+        <v>1255.20718285254</v>
       </c>
       <c r="D700" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E700" s="24" t="n">
         <f aca="false">tp_w_dcf*C700+(1-tp_w_dcf)*D700</f>
-        <v>1009.01237479754</v>
+        <v>1011.06896160273</v>
       </c>
       <c r="F700" s="14" t="n">
         <f aca="false">E700/E$698-1</f>
-        <v>0.0589315138129811</v>
+        <v>0.0591075264195902</v>
       </c>
     </row>
     <row r="701" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53296,19 +53296,19 @@
       </c>
       <c r="C701" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+tp_r)^1+Val!B17/(1+tp_r)^2+Val!B18/(1+tp_r)^3+Val!B11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C16/(1+tp_r)^1+Val!C17/(1+tp_r)^2+Val!C18/(1+tp_r)^3+Val!C11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D16/(1+tp_r)^1+Val!D17/(1+tp_r)^2+Val!D18/(1+tp_r)^3+Val!D11*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1196.9424528361</v>
+        <v>1200.43080905912</v>
       </c>
       <c r="D701" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E701" s="24" t="n">
         <f aca="false">tp_w_dcf*C701+(1-tp_w_dcf)*D701</f>
-        <v>981.752571107345</v>
+        <v>983.680774706023</v>
       </c>
       <c r="F701" s="14" t="n">
         <f aca="false">E701/E$698-1</f>
-        <v>0.0303230785658914</v>
+        <v>0.0304180542086039</v>
       </c>
     </row>
     <row r="702" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53320,19 +53320,19 @@
       </c>
       <c r="C702" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+tp_r)^1+Val!B17/(1+tp_r)^2+Val!B18/(1+tp_r)^3+Val!B11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*MAX(0,Val!C16/(1+tp_r)^1+Val!C17/(1+tp_r)^2+Val!C18/(1+tp_r)^3+Val!C11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*MAX(0,Val!D16/(1+tp_r)^1+Val!D17/(1+tp_r)^2+Val!D18/(1+tp_r)^3+Val!D11*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1099.42681217916</v>
+        <v>1102.42625760076</v>
       </c>
       <c r="D702" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E702" s="24" t="n">
         <f aca="false">tp_w_dcf*C702+(1-tp_w_dcf)*D702</f>
-        <v>932.994750778875</v>
+        <v>934.678498976841</v>
       </c>
       <c r="F702" s="14" t="n">
         <f aca="false">E702/E$698-1</f>
-        <v>-0.0208469504449108</v>
+        <v>-0.0209124494537734</v>
       </c>
     </row>
     <row r="703" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53344,19 +53344,19 @@
       </c>
       <c r="C703" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+tp_r)^1+Val!B17/(1+tp_r)^2+Val!B18/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C16/(1+tp_r)^1+Val!C17/(1+tp_r)^2+Val!C18/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D16/(1+tp_r)^1+Val!D17/(1+tp_r)^2+Val!D18/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1139.15521897662</v>
+        <v>1142.35407989709</v>
       </c>
       <c r="D703" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E703" s="24" t="n">
         <f aca="false">0.3*C703+(1-0.3)*D703</f>
-        <v>878.340448257998</v>
+        <v>879.557742216175</v>
       </c>
       <c r="F703" s="14" t="n">
         <f aca="false">E703/E$698-1</f>
-        <v>-0.0782051798882685</v>
+        <v>-0.0786521393900793</v>
       </c>
     </row>
     <row r="704" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53368,19 +53368,19 @@
       </c>
       <c r="C704" s="24" t="n">
         <f aca="false">(tp_wA*MAX(0,Val!B16/(1+tp_r)^1+Val!B17/(1+tp_r)^2+Val!B18/(1+tp_r)^3+Val!B11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*MAX(0,Val!C16/(1+tp_r)^1+Val!C17/(1+tp_r)^2+Val!C18/(1+tp_r)^3+Val!C11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*MAX(0,Val!D16/(1+tp_r)^1+Val!D17/(1+tp_r)^2+Val!D18/(1+tp_r)^3+Val!D11*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D12*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D13*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D13*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
-        <v>1139.15521897662</v>
+        <v>1142.35407989709</v>
       </c>
       <c r="D704" s="24" t="n">
         <f aca="false">Val!B34</f>
-        <v>766.562689378587</v>
+        <v>766.930740352925</v>
       </c>
       <c r="E704" s="24" t="n">
         <f aca="false">0.7*C704+(1-0.7)*D704</f>
-        <v>1027.37746009721</v>
+        <v>1029.72707803384</v>
       </c>
       <c r="F704" s="14" t="n">
         <f aca="false">E704/E$698-1</f>
-        <v>0.0782051798882684</v>
+        <v>0.0786521393900792</v>
       </c>
     </row>
     <row r="705" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
